--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E98" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Porch Light</v>
+        <v>Riptides</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-16</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>The Great Divide</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G2" t="str">
-        <v>4:22</v>
+        <v>3:17</v>
       </c>
       <c r="H2" t="str">
-        <v>Noah Kahan</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L2" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dry Spell</v>
+        <v>Porch Light</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-16</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Middle of Nowhere</v>
+        <v>The Great Divide</v>
       </c>
       <c r="G3" t="str">
-        <v>3:17</v>
+        <v>4:22</v>
       </c>
       <c r="H3" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Noah Kahan</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
       </c>
       <c r="L3" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Porch Light - Noah Kahan</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>The Visitor</v>
+        <v>Dry Spell</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-16</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>The Visitor - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G4" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H4" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
       </c>
       <c r="L4" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Dry Spell - Kacey Musgraves</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>The Visitor</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-16</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>The Way I Am</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H5" t="str">
-        <v>Luke Combs</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L5" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Can't Sit Still</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-16</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G6" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H6" t="str">
-        <v>Lainey Wilson</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L6" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-16</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:43</v>
+        <v>3:35</v>
       </c>
       <c r="H7" t="str">
-        <v>beabadoobee</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L7" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Blow My Mind</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-16</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Sexistential</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>2:57</v>
+        <v>3:43</v>
       </c>
       <c r="H8" t="str">
-        <v>Robyn</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L8" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SATA</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-16</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Sexistential</v>
       </c>
       <c r="G9" t="str">
-        <v>3:02</v>
+        <v>2:57</v>
       </c>
       <c r="H9" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L9" t="str">
-        <v>SATA - John Summit</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Una Aventura</v>
+        <v>SATA</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-16</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Una Aventura - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G10" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H10" t="str">
-        <v>Ozuna</v>
+        <v>John Summit</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L10" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-16</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:44</v>
+        <v>3:00</v>
       </c>
       <c r="H11" t="str">
-        <v>Charlie Puth</v>
+        <v>Ozuna</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L11" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-16</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G12" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H12" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L12" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-16</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G13" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H13" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L13" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-16</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G14" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H14" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L14" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-16</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H15" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L15" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-16</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G16" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H16" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L16" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-16</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H17" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L17" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-16</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H18" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L18" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-16</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H19" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L19" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-16</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G20" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H20" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L20" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-16</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H21" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L21" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-16</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G22" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H22" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L22" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-16</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H23" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L23" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-16</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G24" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H24" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L24" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-16</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G25" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H25" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L25" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-16</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H26" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L26" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-16</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H27" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L27" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-16</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H28" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L28" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-16</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H29" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L29" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-16</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H30" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L30" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-16</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H31" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L31" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-16</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H32" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L32" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-16</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G33" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H33" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L33" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-16</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G34" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H34" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L34" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-16</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G35" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H35" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L35" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-16</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H36" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L36" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-16</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G37" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H37" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L37" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-16</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H38" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L38" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-16</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G39" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H39" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L39" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-16</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H40" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L40" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-16</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H41" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L41" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-16</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G42" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H42" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L42" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-16</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H43" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L43" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-16</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G44" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H44" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L44" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-16</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G45" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H45" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L45" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-16</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H46" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L46" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-16</v>
@@ -2164,33 +2164,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G47" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H47" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L47" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-16</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G48" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H48" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L48" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-16</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G49" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H49" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L49" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-16</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H50" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L50" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-16</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L51" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-16</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H52" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L52" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-16</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G53" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H53" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L53" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-16</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G54" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H54" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L54" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-16</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G55" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H55" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L55" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-16</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G56" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H56" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L56" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-16</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G57" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H57" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L57" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-16</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H58" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L58" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-16</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H59" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L59" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-16</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G60" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H60" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L60" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-16</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G61" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H61" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L61" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-16</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H62" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L62" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-16</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H63" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L63" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-16</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H64" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L64" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-16</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G65" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H65" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L65" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-16</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H66" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L66" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-16</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H67" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L67" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-16</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H68" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L68" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-16</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H69" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L69" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-16</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H70" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L70" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-16</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G71" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H71" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L71" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-16</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H72" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L72" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-16</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H73" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L73" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-16</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G74" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H74" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L74" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-16</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G75" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H75" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L75" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-16</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G76" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H76" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L76" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-16</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H77" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L77" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-16</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H78" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L78" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-16</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H79" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L79" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-16</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H80" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L80" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-16</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H81" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L81" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-16</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G82" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H82" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L82" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-16</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H83" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L83" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-16</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H84" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L84" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-16</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H85" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L85" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-16</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H86" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L86" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-16</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H87" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L87" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-16</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H88" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L88" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-16</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G89" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H89" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L89" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-16</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H90" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L90" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-16</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H91" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L91" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-16</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H92" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L92" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-16</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H93" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L93" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-16</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H94" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L94" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-16</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G95" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H95" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L95" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-16</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G96" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H96" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L96" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-16</v>
@@ -4061,68 +4061,106 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G97" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H97" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L97" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+      <c r="C98" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G98" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I98" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J98" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K98" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D98" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
+      <c r="D99" t="str">
+        <v>2026-03-16</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G99" t="str">
         <v>4:37</v>
       </c>
-      <c r="H98" t="str">
+      <c r="H99" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I98" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J98" t="str">
+      <c r="I99" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J99" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K98" t="str">
+      <c r="K99" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L98" t="str">
+      <c r="L99" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L99"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E99" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-17</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H2" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L2" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Visitor</v>
+        <v>Riptides</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-17</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>The Visitor - Single</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G5" t="str">
-        <v>3:48</v>
+        <v>3:17</v>
       </c>
       <c r="H5" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L5" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>The Visitor</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-17</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>The Way I Am</v>
+        <v>The Visitor - Single</v>
       </c>
       <c r="G6" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H6" t="str">
-        <v>Luke Combs</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
       </c>
       <c r="L6" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>The Visitor - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Can't Sit Still</v>
+        <v>I Ain't No Cowboy</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-17</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G7" t="str">
-        <v>3:35</v>
+        <v>3:13</v>
       </c>
       <c r="H7" t="str">
-        <v>Lainey Wilson</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
       </c>
       <c r="L7" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>I Ain't No Cowboy - Luke Combs</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>Can't Sit Still</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-17</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>Can't Sit Still - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>3:43</v>
+        <v>3:35</v>
       </c>
       <c r="H8" t="str">
-        <v>beabadoobee</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
       </c>
       <c r="L8" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>Can't Sit Still - Lainey Wilson</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Blow My Mind</v>
+        <v>All I Did Was Dream of You (feat. The Marías)</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D9" t="str">
         <v>2026-03-17</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Sexistential</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>2:57</v>
+        <v>3:43</v>
       </c>
       <c r="H9" t="str">
-        <v>Robyn</v>
+        <v>beabadoobee</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
       </c>
       <c r="L9" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SATA</v>
+        <v>Blow My Mind</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D10" t="str">
         <v>2026-03-17</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Sexistential</v>
       </c>
       <c r="G10" t="str">
-        <v>3:02</v>
+        <v>2:57</v>
       </c>
       <c r="H10" t="str">
-        <v>John Summit</v>
+        <v>Robyn</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/robyn/535211</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
       </c>
       <c r="L10" t="str">
-        <v>SATA - John Summit</v>
+        <v>Blow My Mind - Robyn</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Una Aventura</v>
+        <v>SATA</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D11" t="str">
         <v>2026-03-17</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Una Aventura - Single</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G11" t="str">
-        <v>3:00</v>
+        <v>3:02</v>
       </c>
       <c r="H11" t="str">
-        <v>Ozuna</v>
+        <v>John Summit</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/sata/1874015470</v>
       </c>
       <c r="L11" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>SATA - John Summit</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Una Aventura</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D12" t="str">
         <v>2026-03-17</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Una Aventura - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>3:44</v>
+        <v>3:00</v>
       </c>
       <c r="H12" t="str">
-        <v>Charlie Puth</v>
+        <v>Ozuna</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
       </c>
       <c r="L12" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Una Aventura - Ozuna</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-17</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G13" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H13" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L13" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-17</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G14" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H14" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L14" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-17</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G15" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H15" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L15" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-17</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H16" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L16" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-17</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G17" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H17" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L17" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-17</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H18" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L18" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-17</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H19" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L19" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-17</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H20" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L20" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-17</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G21" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H21" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L21" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-17</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H22" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L22" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-17</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G23" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H23" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L23" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-17</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H24" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L24" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-17</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G25" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H25" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L25" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-17</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G26" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H26" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L26" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-17</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H27" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L27" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-17</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H28" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L28" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-17</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H29" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L29" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-17</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H30" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L30" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-17</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H31" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L31" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-17</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H32" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L32" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-17</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H33" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L33" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-17</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G34" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H34" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L34" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-17</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G35" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H35" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L35" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-17</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G36" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H36" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L36" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-17</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H37" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L37" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-17</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G38" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H38" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L38" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-17</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H39" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L39" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-17</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G40" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H40" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L40" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-17</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H41" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L41" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-17</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H42" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L42" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-17</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G43" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H43" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L43" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-17</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H44" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L44" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-17</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G45" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H45" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L45" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-17</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G46" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H46" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L46" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-17</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H47" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L47" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-17</v>
@@ -2202,33 +2202,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G48" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H48" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L48" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-17</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G49" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H49" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L49" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-17</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G50" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H50" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L50" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-17</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H51" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L51" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-17</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H52" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L52" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-17</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H53" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L53" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-17</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G54" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H54" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L54" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-17</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G55" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H55" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L55" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-17</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G56" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H56" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L56" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-17</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G57" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H57" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L57" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-17</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G58" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H58" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L58" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-17</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H59" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L59" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-17</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H60" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L60" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-17</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G61" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H61" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L61" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-17</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G62" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H62" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L62" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-17</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H63" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L63" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-17</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H64" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L64" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-17</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H65" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L65" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-17</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G66" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H66" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L66" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-17</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H67" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L67" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-17</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H68" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L68" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-17</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H69" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L69" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-17</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H70" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L70" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-17</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H71" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L71" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-17</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G72" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H72" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L72" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-17</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H73" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L73" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-17</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H74" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L74" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-17</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G75" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H75" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L75" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-17</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G76" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H76" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L76" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-17</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G77" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H77" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L77" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-17</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H78" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L78" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-17</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H79" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L79" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-17</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H80" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L80" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-17</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H81" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L81" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-17</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H82" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L82" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-17</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G83" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H83" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L83" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-17</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H84" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L84" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-17</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H85" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L85" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-17</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H86" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L86" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-17</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H87" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L87" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-17</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H88" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L88" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-17</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H89" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L89" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-17</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G90" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H90" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L90" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-17</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H91" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L91" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-17</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H92" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L92" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-17</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H93" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L93" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-17</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H94" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L94" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-17</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H95" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L95" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-17</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G96" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H96" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L96" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-17</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G97" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H97" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L97" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-17</v>
@@ -4099,68 +4099,106 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G98" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H98" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L98" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+      <c r="C99" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G99" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I99" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J99" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K99" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" t="str">
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D99" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
+      <c r="D100" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G99" t="str">
+      <c r="G100" t="str">
         <v>4:37</v>
       </c>
-      <c r="H99" t="str">
+      <c r="H100" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I99" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J99" t="str">
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K99" t="str">
+      <c r="K100" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L99" t="str">
+      <c r="L100" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E100" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-18</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H2" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L2" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-18</v>
@@ -565,25 +565,25 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H5" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L5" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="6">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Riptides</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-18</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Whatever's Clever!</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G13" t="str">
-        <v>3:44</v>
+        <v>3:17</v>
       </c>
       <c r="H13" t="str">
-        <v>Charlie Puth</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L13" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>dirty wedding dress</v>
+        <v>Home (feat. Hikaru Utada)</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D14" t="str">
         <v>2026-03-18</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Whatever's Clever!</v>
       </c>
       <c r="G14" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H14" t="str">
-        <v>Bleachers</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
       </c>
       <c r="L14" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>dirty wedding dress</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D15" t="str">
         <v>2026-03-18</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Age of the Ram</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G15" t="str">
-        <v>3:07</v>
+        <v>4:49</v>
       </c>
       <c r="H15" t="str">
-        <v>Charley Crockett</v>
+        <v>Bleachers</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
       </c>
       <c r="L15" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>dirty wedding dress - Bleachers</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-18</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G16" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H16" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L16" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-18</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H17" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L17" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-18</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G18" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H18" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L18" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-18</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H19" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L19" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-18</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H20" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L20" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-18</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H21" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L21" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-18</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G22" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H22" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L22" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-18</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H23" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L23" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-18</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G24" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H24" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L24" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-18</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H25" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L25" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-18</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G26" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H26" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L26" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-18</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G27" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H27" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L27" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-18</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H28" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L28" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-18</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H29" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L29" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-18</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H30" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L30" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-18</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H31" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L31" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-18</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H32" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L32" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-18</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H33" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L33" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-18</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H34" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L34" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-18</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G35" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H35" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L35" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-18</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G36" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H36" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L36" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-18</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G37" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H37" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L37" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-18</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L38" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-18</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G39" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H39" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L39" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-18</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H40" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L40" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-18</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G41" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H41" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L41" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-18</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H42" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L42" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-18</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H43" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L43" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-18</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G44" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H44" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L44" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-18</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H45" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L45" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-18</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G46" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H46" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L46" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-18</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G47" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H47" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L47" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-18</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H48" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L48" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-18</v>
@@ -2240,33 +2240,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G49" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H49" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L49" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-18</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G50" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H50" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L50" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-18</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G51" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H51" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L51" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-18</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H52" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L52" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-18</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H53" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L53" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-18</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H54" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L54" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-18</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G55" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H55" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L55" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-18</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G56" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H56" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L56" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-18</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G57" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H57" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L57" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-18</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G58" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H58" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L58" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-18</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G59" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H59" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L59" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-18</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H60" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L60" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-18</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H61" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L61" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-18</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G62" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H62" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L62" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-18</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G63" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H63" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L63" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-18</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H64" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L64" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-18</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H65" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L65" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-18</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H66" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L66" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-18</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G67" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H67" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L67" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-18</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H68" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L68" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-18</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H69" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L69" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-18</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H70" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L70" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-18</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H71" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L71" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-18</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H72" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L72" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-18</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G73" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H73" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L73" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-18</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H74" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L74" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-18</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H75" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L75" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-18</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G76" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H76" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L76" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-18</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G77" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H77" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L77" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-18</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G78" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H78" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L78" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-18</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H79" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L79" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-18</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H80" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L80" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-18</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H81" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L81" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-18</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H82" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L82" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-18</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H83" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L83" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-18</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G84" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H84" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L84" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-18</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H85" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L85" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-18</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H86" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L86" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-18</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H87" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L87" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-18</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L88" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-18</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H89" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L89" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-18</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H90" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L90" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-18</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G91" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H91" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L91" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-18</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H92" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L92" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-18</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H93" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L93" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-18</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H94" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L94" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-18</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H95" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L95" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-18</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H96" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L96" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-18</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G97" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H97" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L97" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-18</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G98" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H98" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L98" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-18</v>
@@ -4137,68 +4137,106 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G99" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H99" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L99" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K100" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D100" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
+      <c r="D101" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G101" t="str">
         <v>4:37</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H101" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K100" t="str">
+      <c r="K101" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L100" t="str">
+      <c r="L101" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/porch-light/1872239892</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/sata/1874015489</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Distance</v>
+        <v>Pongo</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-19</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Distance - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:14</v>
+        <v>3:09</v>
       </c>
       <c r="H2" t="str">
-        <v>Finn Askew</v>
+        <v>Rvssian</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L2" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Ocean In The Desert</v>
+        <v>Distance</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-19</v>
@@ -565,25 +565,25 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H5" t="str">
-        <v>Dionne Warwick</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L5" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="6">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Riptides</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/riptides/1878362645</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D13" t="str">
         <v>2026-03-19</v>
@@ -869,25 +869,25 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>I Built You a Tower</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:17</v>
+        <v>3:44</v>
       </c>
       <c r="H13" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/riptides/1878362451</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L13" t="str">
-        <v>Riptides - Death Cab for Cutie</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="14">
@@ -968,13 +968,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>Riptides</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D16" t="str">
         <v>2026-03-19</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Age of the Ram</v>
+        <v>I Built You a Tower</v>
       </c>
       <c r="G16" t="str">
-        <v>3:07</v>
+        <v>3:17</v>
       </c>
       <c r="H16" t="str">
-        <v>Charley Crockett</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/riptides/1878362451</v>
       </c>
       <c r="L16" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>Riptides - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>IMPOSIBLE</v>
+        <v>Fastest Gun Alive</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
       </c>
       <c r="D17" t="str">
         <v>2026-03-19</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>Age of the Ram</v>
       </c>
       <c r="G17" t="str">
-        <v>3:13</v>
+        <v>3:07</v>
       </c>
       <c r="H17" t="str">
-        <v>Grupo Frontera</v>
+        <v>Charley Crockett</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
       </c>
       <c r="L17" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>Fastest Gun Alive - Charley Crockett</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Trade Places</v>
+        <v>IMPOSIBLE</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/imposible/1880775726</v>
       </c>
       <c r="D18" t="str">
         <v>2026-03-19</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Monica</v>
+        <v>IMPOSIBLE - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:02</v>
+        <v>3:13</v>
       </c>
       <c r="H18" t="str">
-        <v>Jack Harlow</v>
+        <v>Grupo Frontera</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/imposible/1880775721</v>
       </c>
       <c r="L18" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>IMPOSIBLE - Grupo Frontera</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Motion Party</v>
+        <v>Trade Places</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
       </c>
       <c r="D19" t="str">
         <v>2026-03-19</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Motion Party - Single</v>
+        <v>Monica</v>
       </c>
       <c r="G19" t="str">
-        <v>1:35</v>
+        <v>3:02</v>
       </c>
       <c r="H19" t="str">
-        <v>Bossman Dlow</v>
+        <v>Jack Harlow</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
       </c>
       <c r="L19" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Trade Places - Jack Harlow</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Woman</v>
+        <v>Motion Party</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
       </c>
       <c r="D20" t="str">
         <v>2026-03-19</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Woman - Single</v>
+        <v>Motion Party - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:46</v>
+        <v>1:35</v>
       </c>
       <c r="H20" t="str">
-        <v>Kane Brown</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
       </c>
       <c r="L20" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>Motion Party - Bossman Dlow</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Sunburn</v>
+        <v>Woman</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/woman/1882549709</v>
       </c>
       <c r="D21" t="str">
         <v>2026-03-19</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Sunburn - Single</v>
+        <v>Woman - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>3:05</v>
+        <v>2:46</v>
       </c>
       <c r="H21" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Kane Brown</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/woman/1882549705</v>
       </c>
       <c r="L21" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Woman - Kane Brown</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Que Te Costó</v>
+        <v>Sunburn</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
       </c>
       <c r="D22" t="str">
         <v>2026-03-19</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Metamorfosis</v>
+        <v>Sunburn - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:54</v>
+        <v>3:05</v>
       </c>
       <c r="H22" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Tucker Wetmore</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
       </c>
       <c r="L22" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Sunburn - Tucker Wetmore</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>oooshxt!</v>
+        <v>Que Te Costó</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
       </c>
       <c r="D23" t="str">
         <v>2026-03-19</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Metamorfosis</v>
       </c>
       <c r="G23" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H23" t="str">
-        <v>Samara Cyn</v>
+        <v>Yahritza Y Su Esencia</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
       </c>
       <c r="L23" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Que Te Costó - Yahritza Y Su Esencia</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt!</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
       </c>
       <c r="D24" t="str">
         <v>2026-03-19</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Cruel World</v>
+        <v>oooshxt! - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:26</v>
+        <v>2:15</v>
       </c>
       <c r="H24" t="str">
-        <v>Holly Humberstone</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
       </c>
       <c r="L24" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>oooshxt! - Samara Cyn</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Star</v>
+        <v>Cruel World</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
       </c>
       <c r="D25" t="str">
         <v>2026-03-19</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Star - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G25" t="str">
-        <v>3:25</v>
+        <v>3:26</v>
       </c>
       <c r="H25" t="str">
-        <v>Iceage</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
       </c>
       <c r="L25" t="str">
-        <v>Star - Iceage</v>
+        <v>Cruel World - Holly Humberstone</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Get Go</v>
+        <v>Star</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/star/1876633306</v>
       </c>
       <c r="D26" t="str">
         <v>2026-03-19</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Star - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:22</v>
+        <v>3:25</v>
       </c>
       <c r="H26" t="str">
-        <v>Arlo Parks</v>
+        <v>Iceage</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/star/1876633303</v>
       </c>
       <c r="L26" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Star - Iceage</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ThunderWave</v>
+        <v>Get Go</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/get-go/1862570884</v>
       </c>
       <c r="D27" t="str">
         <v>2026-03-19</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Distracted</v>
+        <v>Ambiguous Desire</v>
       </c>
       <c r="G27" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H27" t="str">
-        <v>Thundercat</v>
+        <v>Arlo Parks</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/get-go/1862570378</v>
       </c>
       <c r="L27" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Get Go - Arlo Parks</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Club Song</v>
+        <v>ThunderWave</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
       </c>
       <c r="D28" t="str">
         <v>2026-03-19</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Club Song - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G28" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H28" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Thundercat</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
       </c>
       <c r="L28" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>ThunderWave - Thundercat</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Better Man</v>
+        <v>Club Song</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/club-song/1882478246</v>
       </c>
       <c r="D29" t="str">
         <v>2026-03-19</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Better Man - Single</v>
+        <v>Club Song - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:53</v>
+        <v>2:27</v>
       </c>
       <c r="H29" t="str">
-        <v>jxdn</v>
+        <v>The Pussycat Dolls</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/club-song/1882478243</v>
       </c>
       <c r="L29" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Club Song - The Pussycat Dolls</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>sabotage</v>
+        <v>Better Man</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/better-man/1880496044</v>
       </c>
       <c r="D30" t="str">
         <v>2026-03-19</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>sabotage - Single</v>
+        <v>Better Man - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>2:58</v>
+        <v>2:53</v>
       </c>
       <c r="H30" t="str">
-        <v>Natalie Jane</v>
+        <v>jxdn</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/better-man/1880496042</v>
       </c>
       <c r="L30" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>Better Man - jxdn</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>sabotage</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
       </c>
       <c r="D31" t="str">
         <v>2026-03-19</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>sabotage - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H31" t="str">
-        <v>WHATMORE</v>
+        <v>Natalie Jane</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
       </c>
       <c r="L31" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>sabotage - Natalie Jane</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Naked</v>
+        <v>2000s Pop Punk Rnb</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
       </c>
       <c r="D32" t="str">
         <v>2026-03-19</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Naked - Single</v>
+        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:39</v>
+        <v>2:56</v>
       </c>
       <c r="H32" t="str">
-        <v>Kenya Grace</v>
+        <v>WHATMORE</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
       </c>
       <c r="L32" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>2000s Pop Punk Rnb - WHATMORE</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Catharina</v>
+        <v>Naked</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/naked/1883802157</v>
       </c>
       <c r="D33" t="str">
         <v>2026-03-19</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Catharina - Single</v>
+        <v>Naked - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:27</v>
+        <v>3:39</v>
       </c>
       <c r="H33" t="str">
-        <v>Martin Garrix</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/naked/1883801913</v>
       </c>
       <c r="L33" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>Naked - Kenya Grace</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>Catharina</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/catharina/1880130477</v>
       </c>
       <c r="D34" t="str">
         <v>2026-03-19</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>Catharina - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:00</v>
+        <v>3:27</v>
       </c>
       <c r="H34" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/catharina/1880130476</v>
       </c>
       <c r="L34" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>Catharina - Martin Garrix</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer)</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
       </c>
       <c r="D35" t="str">
         <v>2026-03-19</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Trying Times</v>
+        <v>Through The Pain (feat. Pozer) - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>4:33</v>
+        <v>3:00</v>
       </c>
       <c r="H35" t="str">
-        <v>James Blake</v>
+        <v>Chase &amp; Status</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
       </c>
       <c r="L35" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>595</v>
+        <v>Trying Times</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
       </c>
       <c r="D36" t="str">
         <v>2026-03-19</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Trying Times</v>
       </c>
       <c r="G36" t="str">
-        <v>2:29</v>
+        <v>4:33</v>
       </c>
       <c r="H36" t="str">
-        <v>Violet Grohl</v>
+        <v>James Blake</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
       </c>
       <c r="L36" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Trying Times - James Blake</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>595</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/595/1880470541</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-19</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Soft 2</v>
+        <v>Be Sweet To Me</v>
       </c>
       <c r="G37" t="str">
-        <v>3:50</v>
+        <v>2:29</v>
       </c>
       <c r="H37" t="str">
-        <v>LANY</v>
+        <v>Violet Grohl</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/595/1880470537</v>
       </c>
       <c r="L37" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>595 - Violet Grohl</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CALL ME</v>
+        <v>When Did You Stop Loving Me?</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-19</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>CALL ME - Single</v>
+        <v>Soft 2</v>
       </c>
       <c r="G38" t="str">
-        <v>2:10</v>
+        <v>3:50</v>
       </c>
       <c r="H38" t="str">
-        <v>ALTÉGO</v>
+        <v>LANY</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/lany/867853783</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
       </c>
       <c r="L38" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>When Did You Stop Loving Me? - LANY</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Mi Amor</v>
+        <v>CALL ME</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/call-me/1882521075</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-19</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Free (Deluxe)</v>
+        <v>CALL ME - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>2:00</v>
+        <v>2:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Nasty C</v>
+        <v>ALTÉGO</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/call-me/1882521073</v>
       </c>
       <c r="L39" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>CALL ME - ALTÉGO</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>BOBA</v>
+        <v>Mi Amor</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-19</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>BOBA - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G40" t="str">
-        <v>3:00</v>
+        <v>2:00</v>
       </c>
       <c r="H40" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Nasty C</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
       </c>
       <c r="L40" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>Mi Amor - Nasty C</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Video Shoot</v>
+        <v>BOBA</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/boba/1880372256</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-19</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Skeletor</v>
+        <v>BOBA - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:38</v>
+        <v>3:00</v>
       </c>
       <c r="H41" t="str">
-        <v>Chief Keef</v>
+        <v>SOFI TUKKER</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/boba/1880372250</v>
       </c>
       <c r="L41" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>BOBA - SOFI TUKKER</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Video Shoot</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-19</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Skeletor</v>
       </c>
       <c r="G42" t="str">
-        <v>2:06</v>
+        <v>2:38</v>
       </c>
       <c r="H42" t="str">
-        <v>Shenseea</v>
+        <v>Chief Keef</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
       </c>
       <c r="L42" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Video Shoot - Chief Keef</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Just Believe</v>
+        <v>Talk To Me Nuh</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-19</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Just Believe - Single</v>
+        <v>Talk To Me Nuh - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>2:41</v>
+        <v>2:06</v>
       </c>
       <c r="H43" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Shenseea</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
       </c>
       <c r="L43" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>Talk To Me Nuh - Shenseea</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Knife In The Heart</v>
+        <v>Just Believe</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-19</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>The Afterparty</v>
+        <v>Just Believe - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>2:57</v>
+        <v>2:41</v>
       </c>
       <c r="H44" t="str">
-        <v>Lykke Li</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
       </c>
       <c r="L44" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Just Believe - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Way We Touch</v>
+        <v>Knife In The Heart</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-19</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G45" t="str">
-        <v>3:09</v>
+        <v>2:57</v>
       </c>
       <c r="H45" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
       </c>
       <c r="L45" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Knife In The Heart - Lykke Li</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DANGEROUS</v>
+        <v>The Way We Touch</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-19</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>The Way We Touch - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>4:06</v>
+        <v>3:09</v>
       </c>
       <c r="H46" t="str">
-        <v>Magnolia Park</v>
+        <v>Charlotte Cardin</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
       </c>
       <c r="L46" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>The Way We Touch - Charlotte Cardin</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>When I Wake Up</v>
+        <v>DANGEROUS</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-19</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Dear God</v>
+        <v>NIGHTS AFTER VAMP</v>
       </c>
       <c r="G47" t="str">
-        <v>3:33</v>
+        <v>4:06</v>
       </c>
       <c r="H47" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Magnolia Park</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
       </c>
       <c r="L47" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DANGEROUS - Magnolia Park</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Breathe</v>
+        <v>When I Wake Up</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-19</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Breathe - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G48" t="str">
-        <v>2:56</v>
+        <v>3:33</v>
       </c>
       <c r="H48" t="str">
-        <v>Malcolm Todd</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
       </c>
       <c r="L48" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>When I Wake Up - The Pretty Reckless</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Minty</v>
+        <v>Breathe</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/breathe/1882808152</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-19</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Breathe - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>1:47</v>
+        <v>2:56</v>
       </c>
       <c r="H49" t="str">
-        <v>MIKE</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/breathe/1882807987</v>
       </c>
       <c r="L49" t="str">
-        <v>Minty - MIKE</v>
+        <v>Breathe - Malcolm Todd</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Earth</v>
+        <v>Minty</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/minty/1870867418</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-19</v>
@@ -2278,33 +2278,33 @@
         <v>POMPEII // UTILITY</v>
       </c>
       <c r="G50" t="str">
-        <v>1:37</v>
+        <v>1:47</v>
       </c>
       <c r="H50" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>MIKE</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/mike/1253023714</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/minty/1870867411</v>
       </c>
       <c r="L50" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Minty - MIKE</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drink The Water</v>
+        <v>Earth</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/earth/1870867498</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-19</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>POMPEII // UTILITY</v>
       </c>
       <c r="G51" t="str">
-        <v>3:42</v>
+        <v>1:37</v>
       </c>
       <c r="H51" t="str">
-        <v>Jack Johnson</v>
+        <v>Earl Sweatshirt</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/earth/1870867411</v>
       </c>
       <c r="L51" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Earth - Earl Sweatshirt</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Drink The Water</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-19</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G52" t="str">
-        <v>4:32</v>
+        <v>3:42</v>
       </c>
       <c r="H52" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
       </c>
       <c r="L52" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Drink The Water - Jack Johnson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>A Rainy Night in Soho</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-19</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>A Rainy Night in Soho - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:32</v>
+        <v>4:32</v>
       </c>
       <c r="H53" t="str">
-        <v>Carly Pearce</v>
+        <v>Bruce Springsteen</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
       </c>
       <c r="L53" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>A Rainy Night in Soho - Bruce Springsteen</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Muchacho Alegre</v>
+        <v>If I Don't Leave I'm Gonna Stay</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-19</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>If I Don't Leave I'm Gonna Stay - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>3:08</v>
+        <v>3:32</v>
       </c>
       <c r="H54" t="str">
-        <v>Luis R Conriquez</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
       </c>
       <c r="L54" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Real Slow</v>
+        <v>Muchacho Alegre</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-19</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Work of Heart</v>
+        <v>Muchacho Alegre - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:22</v>
+        <v>3:08</v>
       </c>
       <c r="H55" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Luis R Conriquez</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
       </c>
       <c r="L55" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Muchacho Alegre - Luis R Conriquez</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Mountain Girl</v>
+        <v>Real Slow</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-19</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>As Is</v>
+        <v>Work of Heart</v>
       </c>
       <c r="G56" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H56" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>Flatland Cavalry</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
       </c>
       <c r="L56" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Real Slow - Flatland Cavalry</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Like a Spark</v>
+        <v>Mountain Girl</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-19</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>American Stories</v>
+        <v>As Is</v>
       </c>
       <c r="G57" t="str">
-        <v>3:31</v>
+        <v>2:42</v>
       </c>
       <c r="H57" t="str">
-        <v>Rostam</v>
+        <v>Josiah and the Bonnevilles</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
       </c>
       <c r="L57" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Mountain Girl - Josiah and the Bonnevilles</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Cheesecake</v>
+        <v>Like a Spark</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-19</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>American Stories</v>
       </c>
       <c r="G58" t="str">
-        <v>3:29</v>
+        <v>3:31</v>
       </c>
       <c r="H58" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Rostam</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
       </c>
       <c r="L58" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Like a Spark - Rostam</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>Cheesecake</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-19</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>KINDA HARD</v>
+        <v>So Much To Tell You (Deluxe)</v>
       </c>
       <c r="G59" t="str">
-        <v>3:04</v>
+        <v>3:29</v>
       </c>
       <c r="H59" t="str">
-        <v>Bilmuri</v>
+        <v>Ax and the Hatchetmen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
       </c>
       <c r="L59" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>Cheesecake - Ax and the Hatchetmen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Freakin’ Out</v>
+        <v>ALWAYS LET YOU DOWN</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-19</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G60" t="str">
-        <v>3:37</v>
+        <v>3:04</v>
       </c>
       <c r="H60" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
       </c>
       <c r="L60" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Name in Vein</v>
+        <v>Freakin’ Out</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-19</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Name in Vein - Single</v>
+        <v>Freakin’ Out - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:03</v>
+        <v>3:37</v>
       </c>
       <c r="H61" t="str">
-        <v>VOILÀ</v>
+        <v>Dexter and The Moonrocks</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
       </c>
       <c r="L61" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>Freakin’ Out - Dexter and The Moonrocks</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Name in Vein</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-19</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Into Oblivion</v>
+        <v>Name in Vein - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>4:05</v>
+        <v>3:03</v>
       </c>
       <c r="H62" t="str">
-        <v>Lamb of God</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
       </c>
       <c r="L62" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Name in Vein - VOILÀ</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Undefeated Champion</v>
+        <v>St. Catherine's Wheel</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-19</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Sweat</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G63" t="str">
-        <v>3:34</v>
+        <v>4:05</v>
       </c>
       <c r="H63" t="str">
-        <v>Melanie C</v>
+        <v>Lamb of God</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
       </c>
       <c r="L63" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>St. Catherine's Wheel - Lamb of God</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Pull Up</v>
+        <v>Undefeated Champion</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-19</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Pull Up - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G64" t="str">
-        <v>2:35</v>
+        <v>3:34</v>
       </c>
       <c r="H64" t="str">
-        <v>Collect 200</v>
+        <v>Melanie C</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
       </c>
       <c r="L64" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Undefeated Champion - Melanie C</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ranjha</v>
+        <v>Pull Up</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-19</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Ranjha - Single</v>
+        <v>Pull Up - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:04</v>
+        <v>2:35</v>
       </c>
       <c r="H65" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Collect 200</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
       </c>
       <c r="L65" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Pull Up - Collect 200</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>zombies in love</v>
+        <v>Ranjha</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-19</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>zombies in love - Single</v>
+        <v>Ranjha - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H66" t="str">
-        <v>paris jackson</v>
+        <v>Diljit Dosanjh</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
       </c>
       <c r="L66" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>Ranjha - Diljit Dosanjh</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Days Of Us</v>
+        <v>zombies in love</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-19</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Full Circle</v>
+        <v>zombies in love - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>4:39</v>
+        <v>2:53</v>
       </c>
       <c r="H67" t="str">
-        <v>Tom Misch</v>
+        <v>paris jackson</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
       </c>
       <c r="L67" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>zombies in love - paris jackson</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Life Of A Man</v>
+        <v>Days Of Us</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-19</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Full Circle</v>
       </c>
       <c r="G68" t="str">
-        <v>3:15</v>
+        <v>4:39</v>
       </c>
       <c r="H68" t="str">
-        <v>1Ski OG</v>
+        <v>Tom Misch</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
       </c>
       <c r="L68" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>Days Of Us - Tom Misch</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ya No</v>
+        <v>Life Of A Man</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-19</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Ya No - Single</v>
+        <v>Life Of A Man - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H69" t="str">
-        <v>Marca MP</v>
+        <v>1Ski OG</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
       </c>
       <c r="L69" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>Life Of A Man - 1Ski OG</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Ya No</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-19</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>Ya No - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:48</v>
+        <v>3:40</v>
       </c>
       <c r="H70" t="str">
-        <v>Spacey Jane</v>
+        <v>Marca MP</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
       </c>
       <c r="L70" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Ya No - Marca MP</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Relieve You</v>
+        <v>Do You Really Love Her</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-19</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Relieve You - Single</v>
+        <v>Do You Really Love Her - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H71" t="str">
-        <v>4Fargo</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
       </c>
       <c r="L71" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>Do You Really Love Her - Spacey Jane</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Safety</v>
+        <v>Relieve You</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-19</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Safety - Single</v>
+        <v>Relieve You - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:18</v>
+        <v>2:19</v>
       </c>
       <c r="H72" t="str">
-        <v>Lekan</v>
+        <v>4Fargo</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
       </c>
       <c r="L72" t="str">
-        <v>Safety - Lekan</v>
+        <v>Relieve You - 4Fargo</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Starlet</v>
+        <v>Safety</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/safety/1878181748</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-19</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>LK99</v>
+        <v>Safety - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:56</v>
+        <v>3:18</v>
       </c>
       <c r="H73" t="str">
-        <v>Leven Kali</v>
+        <v>Lekan</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/safety/1878181738</v>
       </c>
       <c r="L73" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Safety - Lekan</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Physical</v>
+        <v>Starlet</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/starlet/1873450846</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-19</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Physical - Single</v>
+        <v>LK99</v>
       </c>
       <c r="G74" t="str">
-        <v>3:52</v>
+        <v>2:56</v>
       </c>
       <c r="H74" t="str">
-        <v>Jacquees</v>
+        <v>Leven Kali</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/starlet/1873450570</v>
       </c>
       <c r="L74" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Starlet - Leven Kali</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Physical</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/physical/1883210753</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-19</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Physical - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>4:29</v>
+        <v>3:52</v>
       </c>
       <c r="H75" t="str">
-        <v>Casper Sage</v>
+        <v>Jacquees</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/physical/1883210752</v>
       </c>
       <c r="L75" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Physical - Jacquees</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Regalito</v>
+        <v>i'm dying to feel alive again</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-19</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>TRESCENDER</v>
+        <v>i'm dying to feel alive again - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:41</v>
+        <v>4:29</v>
       </c>
       <c r="H76" t="str">
-        <v>Piso 21</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
       </c>
       <c r="L76" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>i'm dying to feel alive again - Casper Sage</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Cruel Streak</v>
+        <v>Regalito</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/regalito/1880846653</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-19</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>A Pound of Feathers</v>
+        <v>TRESCENDER</v>
       </c>
       <c r="G77" t="str">
-        <v>4:09</v>
+        <v>2:41</v>
       </c>
       <c r="H77" t="str">
-        <v>The Black Crowes</v>
+        <v>Piso 21</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/regalito/1880845994</v>
       </c>
       <c r="L77" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Regalito - Piso 21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Die Young</v>
+        <v>Cruel Streak</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-19</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Little Wide Open</v>
+        <v>A Pound of Feathers</v>
       </c>
       <c r="G78" t="str">
-        <v>3:52</v>
+        <v>4:09</v>
       </c>
       <c r="H78" t="str">
-        <v>Kevin Morby</v>
+        <v>The Black Crowes</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
       </c>
       <c r="L78" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Cruel Streak - The Black Crowes</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Island Girl</v>
+        <v>Die Young</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/die-young/1870715300</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-19</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Island Girl - Single</v>
+        <v>Little Wide Open</v>
       </c>
       <c r="G79" t="str">
-        <v>3:27</v>
+        <v>3:52</v>
       </c>
       <c r="H79" t="str">
-        <v>Pia Mia</v>
+        <v>Kevin Morby</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/die-young/1870715298</v>
       </c>
       <c r="L79" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>Die Young - Kevin Morby</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Island Girl</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-19</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>Island Girl - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:20</v>
+        <v>3:27</v>
       </c>
       <c r="H80" t="str">
-        <v>Claudia Valentina</v>
+        <v>Pia Mia</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
       </c>
       <c r="L80" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Island Girl - Pia Mia</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>GIRLY THINGS</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-19</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>GIRLY THINGS - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:22</v>
+        <v>2:20</v>
       </c>
       <c r="H81" t="str">
-        <v>Shaggy</v>
+        <v>Claudia Valentina</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
       </c>
       <c r="L81" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>GIRLY THINGS - Claudia Valentina</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Tommy’s Song</v>
+        <v>Looking Lovely (feat. Robin Thicke)</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-19</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Lovers - Single</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:44</v>
+        <v>3:22</v>
       </c>
       <c r="H82" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Shaggy</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/shaggy/68616</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
       </c>
       <c r="L82" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Rainbows</v>
+        <v>Tommy’s Song</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-19</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lovers - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:25</v>
+        <v>3:44</v>
       </c>
       <c r="H83" t="str">
-        <v>Allison Russell</v>
+        <v>Nathaniel Rateliff</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
       </c>
       <c r="L83" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Tommy’s Song - Nathaniel Rateliff</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>butterflies</v>
+        <v>Rainbows</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-19</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Rainbows - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:48</v>
+        <v>3:25</v>
       </c>
       <c r="H84" t="str">
-        <v>runo plum</v>
+        <v>Allison Russell</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
       </c>
       <c r="L84" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Rainbows - Allison Russell</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>You're Right</v>
+        <v>butterflies</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-19</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>You're Right - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G85" t="str">
-        <v>3:00</v>
+        <v>2:48</v>
       </c>
       <c r="H85" t="str">
-        <v>Emma Harner</v>
+        <v>runo plum</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
       </c>
       <c r="L85" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>butterflies - runo plum</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bible Belt</v>
+        <v>You're Right</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-19</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Bible Belt - Single</v>
+        <v>You're Right - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:34</v>
+        <v>3:00</v>
       </c>
       <c r="H86" t="str">
-        <v>Baby Bugs</v>
+        <v>Emma Harner</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
       </c>
       <c r="L86" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>You're Right - Emma Harner</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Daze</v>
+        <v>Bible Belt</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-19</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Daze - Single</v>
+        <v>Bible Belt - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:22</v>
+        <v>3:34</v>
       </c>
       <c r="H87" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Baby Bugs</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
       </c>
       <c r="L87" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>Bible Belt - Baby Bugs</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Passionfruit</v>
+        <v>Daze</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/daze/1862607801</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-19</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Passionfruit - Single</v>
+        <v>Daze - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>3:22</v>
       </c>
       <c r="H88" t="str">
-        <v>Anish Kumar</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/daze/1862607800</v>
       </c>
       <c r="L88" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>Daze - Olympia Vitalis</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Madan</v>
+        <v>Passionfruit</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-19</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Madan - Single</v>
+        <v>Passionfruit - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:56</v>
+        <v>3:57</v>
       </c>
       <c r="H89" t="str">
-        <v>Jonas Blue</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
       </c>
       <c r="L89" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Passionfruit - Anish Kumar</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bad Bitch</v>
+        <v>Madan</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/madan/1879822223</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-19</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Madan - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>2:28</v>
+        <v>2:56</v>
       </c>
       <c r="H90" t="str">
-        <v>41</v>
+        <v>Jonas Blue</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/madan/1879822222</v>
       </c>
       <c r="L90" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Madan - Jonas Blue</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Shame</v>
+        <v>Bad Bitch</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-19</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Bad Bitch - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:36</v>
+        <v>2:28</v>
       </c>
       <c r="H91" t="str">
-        <v>Sunday (1994)</v>
+        <v>41</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/41/1688992229</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
       </c>
       <c r="L91" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Bad Bitch - 41</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>teach you to love me</v>
+        <v>Shame</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/shame/1874080307</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-19</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Devotion [Deluxe]</v>
       </c>
       <c r="G92" t="str">
-        <v>3:09</v>
+        <v>3:36</v>
       </c>
       <c r="H92" t="str">
-        <v>Hailey Picardi</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/shame/1874080202</v>
       </c>
       <c r="L92" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Shame - Sunday (1994)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>The Fix</v>
+        <v>teach you to love me</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-19</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>The Fix - Single</v>
+        <v>teach you to love me - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:42</v>
+        <v>3:09</v>
       </c>
       <c r="H93" t="str">
-        <v>Baby J</v>
+        <v>Hailey Picardi</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
       </c>
       <c r="L93" t="str">
-        <v>The Fix - Baby J</v>
+        <v>teach you to love me - Hailey Picardi</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Hanging on Hope</v>
+        <v>The Fix</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-19</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>The Fix - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:43</v>
+        <v>2:42</v>
       </c>
       <c r="H94" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Baby J</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
       </c>
       <c r="L94" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>The Fix - Baby J</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Hanging on Hope</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-19</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Hanging on Hope - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:18</v>
+        <v>3:43</v>
       </c>
       <c r="H95" t="str">
-        <v>Active Child</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
       </c>
       <c r="L95" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Hanging on Hope - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Feel Something</v>
+        <v>I Know What to Say Now</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-19</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Feel Something - Single</v>
+        <v>I Know What to Say Now - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:09</v>
+        <v>3:18</v>
       </c>
       <c r="H96" t="str">
-        <v>Baby Queen</v>
+        <v>Active Child</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/active-child/355288617</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
       </c>
       <c r="L96" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>I Know What to Say Now - Active Child</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>You Or Me</v>
+        <v>Feel Something</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-19</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Good God / Baad Man</v>
+        <v>Feel Something - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>5:28</v>
+        <v>3:09</v>
       </c>
       <c r="H97" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
       </c>
       <c r="L97" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>Feel Something - Baby Queen</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Mortercheyn</v>
+        <v>You Or Me</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-19</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Coronach</v>
+        <v>Good God / Baad Man</v>
       </c>
       <c r="G98" t="str">
-        <v>4:18</v>
+        <v>5:28</v>
       </c>
       <c r="H98" t="str">
-        <v>Hellripper</v>
+        <v>Corrosion of Conformity</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
       </c>
       <c r="L98" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>You Or Me - Corrosion of Conformity</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Rip The God</v>
+        <v>Mortercheyn</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-19</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Coronach</v>
       </c>
       <c r="G99" t="str">
-        <v>5:20</v>
+        <v>4:18</v>
       </c>
       <c r="H99" t="str">
-        <v>Melvins</v>
+        <v>Hellripper</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
       </c>
       <c r="L99" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Mortercheyn - Hellripper</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Who We Are</v>
+        <v>Rip The God</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-19</v>
@@ -4175,68 +4175,106 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Who We Are - Single</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G100" t="str">
-        <v>2:10</v>
+        <v>5:20</v>
       </c>
       <c r="H100" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Melvins</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
       </c>
       <c r="L100" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
+        <v>Rip The God - Melvins</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>Who We Are</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>Who We Are - Single</v>
+      </c>
+      <c r="G101" t="str">
+        <v>2:10</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Kaleena Zanders</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Who We Are - Kaleena Zanders</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>Reels in 360</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
         <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D102" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
         <v>Dying Is The Internet</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G102" t="str">
         <v>4:37</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H102" t="str">
         <v>Simo Cell</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
         <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K102" t="str">
         <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L102" t="str">
         <v>Reels in 360 - Simo Cell</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,534 +436,534 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Pongo</v>
+        <v>SWIM</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/pongo/1882157609</v>
+        <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Pongo - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G2" t="str">
-        <v>3:09</v>
+        <v>2:39</v>
       </c>
       <c r="H2" t="str">
-        <v>Rvssian</v>
+        <v>BTS</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/pongo/1882157603</v>
+        <v>https://music.apple.com/us/album/swim/1868862375</v>
       </c>
       <c r="L2" t="str">
-        <v>Pongo - Rvssian</v>
+        <v>SWIM - BTS</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Porch Light</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer)</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/porch-light/1872239892</v>
+        <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>The Great Divide</v>
+        <v>THIS MUSIC MAY CONTAIN HOPE.</v>
       </c>
       <c r="G3" t="str">
-        <v>4:22</v>
+        <v>5:01</v>
       </c>
       <c r="H3" t="str">
-        <v>Noah Kahan</v>
+        <v>RAYE</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/noah-kahan/328583953</v>
+        <v>https://music.apple.com/us/artist/raye/261686</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/porch-light/1872239868</v>
+        <v>https://music.apple.com/us/album/click-clack-symphony-feat-hans-zimmer/1871085677</v>
       </c>
       <c r="L3" t="str">
-        <v>Porch Light - Noah Kahan</v>
+        <v>Click Clack Symphony. (feat. Hans Zimmer) - RAYE</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dry Spell</v>
+        <v>Loving Life Again</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/dry-spell/1883177258</v>
+        <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Dandelion</v>
       </c>
       <c r="G4" t="str">
-        <v>3:17</v>
+        <v>3:46</v>
       </c>
       <c r="H4" t="str">
-        <v>Kacey Musgraves</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/dry-spell/1883176984</v>
+        <v>https://music.apple.com/us/album/loving-life-again/1869436835</v>
       </c>
       <c r="L4" t="str">
-        <v>Dry Spell - Kacey Musgraves</v>
+        <v>Loving Life Again - Ella Langley</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Distance</v>
+        <v>Rethink Some Things</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/distance/1882713727</v>
+        <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Distance - Single</v>
+        <v>The Way I Am</v>
       </c>
       <c r="G5" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H5" t="str">
-        <v>Finn Askew</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
+        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/distance/1882713721</v>
+        <v>https://music.apple.com/us/album/rethink-some-things/1862634688</v>
       </c>
       <c r="L5" t="str">
-        <v>Distance - Finn Askew</v>
+        <v>Rethink Some Things - Luke Combs</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Visitor</v>
+        <v>TRANKAITO</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/the-visitor/1882146993</v>
+        <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>The Visitor - Single</v>
+        <v>EL GREEN PRINT: La Saga (Disc 1) — FEID VS FERXXO</v>
       </c>
       <c r="G6" t="str">
-        <v>3:48</v>
+        <v>2:42</v>
       </c>
       <c r="H6" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Feid</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/sienna-spiro/1745678083</v>
+        <v>https://music.apple.com/us/artist/feid/194502100</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/the-visitor/1882146992</v>
+        <v>https://music.apple.com/us/album/trankaito/1886206566</v>
       </c>
       <c r="L6" t="str">
-        <v>The Visitor - SIENNA SPIRO</v>
+        <v>TRANKAITO - Feid</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>I Ain't No Cowboy</v>
+        <v>Leak It</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/i-aint-no-cowboy/1862634799</v>
+        <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>The Way I Am</v>
+        <v>Leak It - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:13</v>
+        <v>3:03</v>
       </c>
       <c r="H7" t="str">
-        <v>Luke Combs</v>
+        <v>FLO</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/luke-combs/815635315</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/i-aint-no-cowboy/1862634688</v>
+        <v>https://music.apple.com/us/album/leak-it/1881685398</v>
       </c>
       <c r="L7" t="str">
-        <v>I Ain't No Cowboy - Luke Combs</v>
+        <v>Leak It - FLO</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Can't Sit Still</v>
+        <v>LUVAGIRL</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/cant-sit-still/1878782917</v>
+        <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Can't Sit Still - Single</v>
+        <v>LUVAGIRL - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>3:35</v>
+        <v>2:40</v>
       </c>
       <c r="H8" t="str">
-        <v>Lainey Wilson</v>
+        <v>Coco Jones</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/coco-jones/401400095</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/cant-sit-still/1878782913</v>
+        <v>https://music.apple.com/us/album/luvagirl/1882867560</v>
       </c>
       <c r="L8" t="str">
-        <v>Can't Sit Still - Lainey Wilson</v>
+        <v>LUVAGIRL - Coco Jones</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías)</v>
+        <v>D33P3R</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245797</v>
+        <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - Single</v>
+        <v>R3SET</v>
       </c>
       <c r="G9" t="str">
-        <v>3:43</v>
+        <v>3:25</v>
       </c>
       <c r="H9" t="str">
-        <v>beabadoobee</v>
+        <v>Mike WiLL Made-It</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/beabadoobee/1307650474</v>
+        <v>https://music.apple.com/us/artist/mike-will-made-it/511333957</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/all-i-did-was-dream-of-you-feat-the-mar%C3%ADas/1882245651</v>
+        <v>https://music.apple.com/us/album/d33p3r/1876874349</v>
       </c>
       <c r="L9" t="str">
-        <v>All I Did Was Dream of You (feat. The Marías) - beabadoobee</v>
+        <v>D33P3R - Mike WiLL Made-It</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Blow My Mind</v>
+        <v>Let King Tonka Talk</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/blow-my-mind/1852752616</v>
+        <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Sexistential</v>
+        <v>Let King Tonka Talk - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>2:57</v>
+        <v>3:01</v>
       </c>
       <c r="H10" t="str">
-        <v>Robyn</v>
+        <v>Yeat</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/robyn/535211</v>
+        <v>https://music.apple.com/us/artist/yeat/1318094493</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/blow-my-mind/1852752613</v>
+        <v>https://music.apple.com/us/album/let-king-tonka-talk/1886559003</v>
       </c>
       <c r="L10" t="str">
-        <v>Blow My Mind - Robyn</v>
+        <v>Let King Tonka Talk - Yeat</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SATA</v>
+        <v>Don't Hate Me</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/sata/1874015489</v>
+        <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>Don't Hate Me - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:02</v>
+        <v>3:09</v>
       </c>
       <c r="H11" t="str">
-        <v>John Summit</v>
+        <v>Miles Caton</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/miles-caton/1674606130</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/sata/1874015470</v>
+        <v>https://music.apple.com/us/album/dont-hate-me/1886125790</v>
       </c>
       <c r="L11" t="str">
-        <v>SATA - John Summit</v>
+        <v>Don't Hate Me - Miles Caton</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Una Aventura</v>
+        <v>Pongo</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/una-aventura/1882069505</v>
+        <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>Una Aventura - Single</v>
+        <v>Pongo - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>3:00</v>
+        <v>3:09</v>
       </c>
       <c r="H12" t="str">
-        <v>Ozuna</v>
+        <v>Rvssian</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/rvssian/628716915</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/una-aventura/1882068957</v>
+        <v>https://music.apple.com/us/album/pongo/1882157603</v>
       </c>
       <c r="L12" t="str">
-        <v>Una Aventura - Ozuna</v>
+        <v>Pongo - Rvssian</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ocean In The Desert</v>
+        <v>BOTERO</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
+        <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>Ocean In The Desert - Single</v>
+        <v>BOTERO - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:44</v>
+        <v>4:14</v>
       </c>
       <c r="H13" t="str">
-        <v>Dionne Warwick</v>
+        <v>Maluma</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
+        <v>https://music.apple.com/us/album/botero/1884672851</v>
       </c>
       <c r="L13" t="str">
-        <v>Ocean In The Desert - Dionne Warwick</v>
+        <v>BOTERO - Maluma</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Home (feat. Hikaru Utada)</v>
+        <v>Distance</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/home-feat-hikaru-utada/1845190340</v>
+        <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>Whatever's Clever!</v>
+        <v>Distance - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:44</v>
+        <v>3:14</v>
       </c>
       <c r="H14" t="str">
-        <v>Charlie Puth</v>
+        <v>Finn Askew</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/charlie-puth/336249253</v>
+        <v>https://music.apple.com/us/artist/finn-askew/1292169978</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/home-feat-hikaru-utada/1845189970</v>
+        <v>https://music.apple.com/us/album/distance/1882713721</v>
       </c>
       <c r="L14" t="str">
-        <v>Home (feat. Hikaru Utada) - Charlie Puth</v>
+        <v>Distance - Finn Askew</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>dirty wedding dress</v>
+        <v>Ocean In The Desert</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/dirty-wedding-dress/1872842320</v>
+        <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Ocean In The Desert - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>4:49</v>
+        <v>3:44</v>
       </c>
       <c r="H15" t="str">
-        <v>Bleachers</v>
+        <v>Dionne Warwick</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/dionne-warwick/16198</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/dirty-wedding-dress/1872842313</v>
+        <v>https://music.apple.com/us/album/ocean-in-the-desert/1878421568</v>
       </c>
       <c r="L15" t="str">
-        <v>dirty wedding dress - Bleachers</v>
+        <v>Ocean In The Desert - Dionne Warwick</v>
       </c>
     </row>
     <row r="16">
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1006,3275 +1006,3237 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Fastest Gun Alive</v>
+        <v>2.0</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/fastest-gun-alive/1874700373</v>
+        <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Age of the Ram</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G17" t="str">
-        <v>3:07</v>
+        <v>2:49</v>
       </c>
       <c r="H17" t="str">
-        <v>Charley Crockett</v>
+        <v>BTS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/charley-crockett/987849844</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/fastest-gun-alive/1874700242</v>
+        <v>https://music.apple.com/us/album/2-0/1868862375</v>
       </c>
       <c r="L17" t="str">
-        <v>Fastest Gun Alive - Charley Crockett</v>
+        <v>2.0 - BTS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>IMPOSIBLE</v>
+        <v>6IXER PARTY</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/imposible/1880775726</v>
+        <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>IMPOSIBLE - Single</v>
+        <v>6WA</v>
       </c>
       <c r="G18" t="str">
-        <v>3:13</v>
+        <v>3:08</v>
       </c>
       <c r="H18" t="str">
-        <v>Grupo Frontera</v>
+        <v>BigXthaPlug</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/grupo-frontera/1613772487</v>
+        <v>https://music.apple.com/us/artist/bigxthaplug/1482508209</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/imposible/1880775721</v>
+        <v>https://music.apple.com/us/album/6ixer-party/1880492397</v>
       </c>
       <c r="L18" t="str">
-        <v>IMPOSIBLE - Grupo Frontera</v>
+        <v>6IXER PARTY - BigXthaPlug</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Trade Places</v>
+        <v>Highest</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/trade-places/1878823464</v>
+        <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Monica</v>
+        <v>Detour</v>
       </c>
       <c r="G19" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H19" t="str">
-        <v>Jack Harlow</v>
+        <v>Samara Cyn</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/jack-harlow/1047679432</v>
+        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/trade-places/1878823462</v>
+        <v>https://music.apple.com/us/album/highest/1882161774</v>
       </c>
       <c r="L19" t="str">
-        <v>Trade Places - Jack Harlow</v>
+        <v>Highest - Samara Cyn</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Motion Party</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/motion-party/1882152039</v>
+        <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Motion Party - Single</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>1:35</v>
+        <v>2:40</v>
       </c>
       <c r="H20" t="str">
-        <v>Bossman Dlow</v>
+        <v>Coi Leray</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/coi-leray/1358539712</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/motion-party/1882151996</v>
+        <v>https://music.apple.com/us/album/better-than-yours-feat-youngboy-never-broke-again/1885597834</v>
       </c>
       <c r="L20" t="str">
-        <v>Motion Party - Bossman Dlow</v>
+        <v>Better Than Yours (feat. YoungBoy Never Broke Again) - Coi Leray</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Woman</v>
+        <v>So What</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/woman/1882549709</v>
+        <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Woman - Single</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G21" t="str">
-        <v>2:46</v>
+        <v>4:31</v>
       </c>
       <c r="H21" t="str">
-        <v>Kane Brown</v>
+        <v>MUNA</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/kane-brown/930928857</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/woman/1882549705</v>
+        <v>https://music.apple.com/us/album/so-what/1870702692</v>
       </c>
       <c r="L21" t="str">
-        <v>Woman - Kane Brown</v>
+        <v>So What - MUNA</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Sunburn</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio)</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/sunburn/1880836041</v>
+        <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Sunburn - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G22" t="str">
-        <v>3:05</v>
+        <v>3:12</v>
       </c>
       <c r="H22" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Eli</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/tucker-wetmore/1486724646</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/sunburn/1880835818</v>
+        <v>https://music.apple.com/us/album/girl-of-your-dreams-live-at-apple-music-radio/1886190879</v>
       </c>
       <c r="L22" t="str">
-        <v>Sunburn - Tucker Wetmore</v>
+        <v>Girl of Your Dreams (Live at Apple Music Radio) - Eli</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Que Te Costó</v>
+        <v>Running To Pain</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/que-te-cost%C3%B3/1882108997</v>
+        <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Metamorfosis</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G23" t="str">
-        <v>2:54</v>
+        <v>4:06</v>
       </c>
       <c r="H23" t="str">
-        <v>Yahritza Y Su Esencia</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/yahritza-y-su-esencia/1613375172</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/que-te-cost%C3%B3/1882108989</v>
+        <v>https://music.apple.com/us/album/running-to-pain/1876521144</v>
       </c>
       <c r="L23" t="str">
-        <v>Que Te Costó - Yahritza Y Su Esencia</v>
+        <v>Running To Pain - Kelsey Lu</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>oooshxt!</v>
+        <v>Pinterest (Spanish)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/oooshxt/1879612533</v>
+        <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>oooshxt! - Single</v>
+        <v>Pinterest (Spanish) - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>2:15</v>
+        <v>2:14</v>
       </c>
       <c r="H24" t="str">
-        <v>Samara Cyn</v>
+        <v>Anitta</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/samara-cyn/1476945235</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/oooshxt/1879612532</v>
+        <v>https://music.apple.com/us/album/pinterest-spanish/1885472605</v>
       </c>
       <c r="L24" t="str">
-        <v>oooshxt! - Samara Cyn</v>
+        <v>Pinterest (Spanish) - Anitta</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Cruel World</v>
+        <v>Business &amp; Personal (Intro)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/cruel-world/1859630041</v>
+        <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Cruel World</v>
+        <v>Big Mama</v>
       </c>
       <c r="G25" t="str">
-        <v>3:26</v>
+        <v>4:20</v>
       </c>
       <c r="H25" t="str">
-        <v>Holly Humberstone</v>
+        <v>Latto</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/latto/419799506</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/cruel-world/1859629846</v>
+        <v>https://music.apple.com/us/album/business-personal-intro/1886538932</v>
       </c>
       <c r="L25" t="str">
-        <v>Cruel World - Holly Humberstone</v>
+        <v>Business &amp; Personal (Intro) - Latto</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Star</v>
+        <v>Bird Flu</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/star/1876633306</v>
+        <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Star - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G26" t="str">
-        <v>3:25</v>
+        <v>2:58</v>
       </c>
       <c r="H26" t="str">
-        <v>Iceage</v>
+        <v>6LACK</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/star/1876633303</v>
+        <v>https://music.apple.com/us/album/bird-flu/1884792154</v>
       </c>
       <c r="L26" t="str">
-        <v>Star - Iceage</v>
+        <v>Bird Flu - 6LACK</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Get Go</v>
+        <v>Lighter</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/get-go/1862570884</v>
+        <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Ambiguous Desire</v>
+        <v>Lighter (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H27" t="str">
-        <v>Arlo Parks</v>
+        <v>Jelly Roll</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/arlo-parks/1291875084</v>
+        <v>https://music.apple.com/us/artist/jelly-roll/30624911</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/get-go/1862570378</v>
+        <v>https://music.apple.com/us/album/lighter/1884704631</v>
       </c>
       <c r="L27" t="str">
-        <v>Get Go - Arlo Parks</v>
+        <v>Lighter - Jelly Roll</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ThunderWave</v>
+        <v>Wide Awake</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/thunderwave/1861531685</v>
+        <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Distracted</v>
+        <v>Wide Awake - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:14</v>
+        <v>4:16</v>
       </c>
       <c r="H28" t="str">
-        <v>Thundercat</v>
+        <v>Chris Stussy</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/chris-stussy/746159191</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/thunderwave/1861531667</v>
+        <v>https://music.apple.com/us/album/wide-awake/1881700618</v>
       </c>
       <c r="L28" t="str">
-        <v>ThunderWave - Thundercat</v>
+        <v>Wide Awake - Chris Stussy</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Club Song</v>
+        <v>Don’t Make Me Love U</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/club-song/1882478246</v>
+        <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Club Song - Single</v>
+        <v>Don’t Make Me Love U - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:27</v>
+        <v>3:25</v>
       </c>
       <c r="H29" t="str">
-        <v>The Pussycat Dolls</v>
+        <v>Lizzo</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/the-pussycat-dolls/23331509</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/club-song/1882478243</v>
+        <v>https://music.apple.com/us/album/dont-make-me-love-u/1885895026</v>
       </c>
       <c r="L29" t="str">
-        <v>Club Song - The Pussycat Dolls</v>
+        <v>Don’t Make Me Love U - Lizzo</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Better Man</v>
+        <v>Dinner Party</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/better-man/1880496044</v>
+        <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Better Man - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G30" t="str">
-        <v>2:53</v>
+        <v>2:34</v>
       </c>
       <c r="H30" t="str">
-        <v>jxdn</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/jxdn/1513237359</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/better-man/1880496042</v>
+        <v>https://music.apple.com/us/album/dinner-party/1884418567</v>
       </c>
       <c r="L30" t="str">
-        <v>Better Man - jxdn</v>
+        <v>Dinner Party - Niall Horan</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>sabotage</v>
+        <v>NORMAL</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/sabotage/1882209853</v>
+        <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>sabotage - Single</v>
+        <v>ARIRANG</v>
       </c>
       <c r="G31" t="str">
-        <v>2:58</v>
+        <v>3:01</v>
       </c>
       <c r="H31" t="str">
-        <v>Natalie Jane</v>
+        <v>BTS</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/natalie-jane/1504380197</v>
+        <v>https://music.apple.com/us/artist/bts/883131348</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/sabotage/1882209670</v>
+        <v>https://music.apple.com/us/album/normal/1868862375</v>
       </c>
       <c r="L31" t="str">
-        <v>sabotage - Natalie Jane</v>
+        <v>NORMAL - BTS</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2000s Pop Punk Rnb</v>
+        <v>Die Living</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/2000s-pop-punk-rnb/1878820143</v>
+        <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Still Loiteringgg / 2000s Pop Punk Rnb - Single</v>
+        <v>Die Living - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H32" t="str">
-        <v>WHATMORE</v>
+        <v>ILLENIUM</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/whatmore/1797119133</v>
+        <v>https://music.apple.com/us/artist/illenium/645420096</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/2000s-pop-punk-rnb/1878820131</v>
+        <v>https://music.apple.com/us/album/die-living/1884752887</v>
       </c>
       <c r="L32" t="str">
-        <v>2000s Pop Punk Rnb - WHATMORE</v>
+        <v>Die Living - ILLENIUM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Naked</v>
+        <v>Heaven On Earth</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/naked/1883802157</v>
+        <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Naked - Single</v>
+        <v>Heaven On Earth - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:39</v>
+        <v>2:59</v>
       </c>
       <c r="H33" t="str">
-        <v>Kenya Grace</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/pentatonix/466047278</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/naked/1883801913</v>
+        <v>https://music.apple.com/us/album/heaven-on-earth/1882808095</v>
       </c>
       <c r="L33" t="str">
-        <v>Naked - Kenya Grace</v>
+        <v>Heaven On Earth - Pentatonix</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Catharina</v>
+        <v>an apple a day</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/catharina/1880130477</v>
+        <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Catharina - Single</v>
+        <v>an apple a day - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:27</v>
+        <v>5:16</v>
       </c>
       <c r="H34" t="str">
-        <v>Martin Garrix</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/martin-garrix/430932944</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/catharina/1880130476</v>
+        <v>https://music.apple.com/us/album/an-apple-a-day/1885590042</v>
       </c>
       <c r="L34" t="str">
-        <v>Catharina - Martin Garrix</v>
+        <v>an apple a day - horsegiirL</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Through The Pain (feat. Pozer)</v>
+        <v>OUT LATE.</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/through-the-pain-feat-pozer/1877868063</v>
+        <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Through The Pain (feat. Pozer) - Single</v>
+        <v>OUT LATE. - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:00</v>
+        <v>2:09</v>
       </c>
       <c r="H35" t="str">
-        <v>Chase &amp; Status</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/chase-status/121546679</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/through-the-pain-feat-pozer/1877868059</v>
+        <v>https://music.apple.com/us/album/out-late/1884478038</v>
       </c>
       <c r="L35" t="str">
-        <v>Through The Pain (feat. Pozer) - Chase &amp; Status</v>
+        <v>OUT LATE. - Loud Luxury</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Trying Times</v>
+        <v>Be With You</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/trying-times/1862353792</v>
+        <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Trying Times</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G36" t="str">
-        <v>4:33</v>
+        <v>3:35</v>
       </c>
       <c r="H36" t="str">
-        <v>James Blake</v>
+        <v>Muse</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/trying-times/1862353780</v>
+        <v>https://music.apple.com/us/album/be-with-you/1885607338</v>
       </c>
       <c r="L36" t="str">
-        <v>Trying Times - James Blake</v>
+        <v>Be With You - Muse</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>595</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/595/1880470541</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Be Sweet To Me</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G37" t="str">
-        <v>2:29</v>
+        <v>4:02</v>
       </c>
       <c r="H37" t="str">
-        <v>Violet Grohl</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/violet-grohl/1538671509</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/595/1880470537</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L37" t="str">
-        <v>595 - Violet Grohl</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>When Did You Stop Loving Me?</v>
+        <v>Little by Little</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/when-did-you-stop-loving-me/1879593803</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Soft 2</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:50</v>
+        <v>2:34</v>
       </c>
       <c r="H38" t="str">
-        <v>LANY</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/lany/867853783</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/when-did-you-stop-loving-me/1879593289</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L38" t="str">
-        <v>When Did You Stop Loving Me? - LANY</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CALL ME</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/call-me/1882521075</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>CALL ME - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G39" t="str">
-        <v>2:10</v>
+        <v>3:28</v>
       </c>
       <c r="H39" t="str">
-        <v>ALTÉGO</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/alt%C3%A9go/1606418899</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/call-me/1882521073</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L39" t="str">
-        <v>CALL ME - ALTÉGO</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mi Amor</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/mi-amor/1872454951</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>2:00</v>
+        <v>2:46</v>
       </c>
       <c r="H40" t="str">
-        <v>Nasty C</v>
+        <v>Alok</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/mi-amor/1872454582</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L40" t="str">
-        <v>Mi Amor - Nasty C</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>BOBA</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/boba/1880372256</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>BOBA - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G41" t="str">
-        <v>3:00</v>
+        <v>2:40</v>
       </c>
       <c r="H41" t="str">
-        <v>SOFI TUKKER</v>
+        <v>Artemas</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/sofi-tukker/998656537</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/boba/1880372250</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L41" t="str">
-        <v>BOBA - SOFI TUKKER</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Video Shoot</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/video-shoot/1882892621</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Skeletor</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>2:38</v>
+        <v>2:43</v>
       </c>
       <c r="H42" t="str">
-        <v>Chief Keef</v>
+        <v>Asake</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/chief-keef/516663045</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/video-shoot/1882892614</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L42" t="str">
-        <v>Video Shoot - Chief Keef</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Talk To Me Nuh</v>
+        <v>Honest</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/talk-to-me-nuh/1882510363</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Talk To Me Nuh - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>2:06</v>
+        <v>3:22</v>
       </c>
       <c r="H43" t="str">
-        <v>Shenseea</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/shenseea/1132311326</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/talk-to-me-nuh/1882510361</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L43" t="str">
-        <v>Talk To Me Nuh - Shenseea</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Just Believe</v>
+        <v>6ft Under</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/just-believe/1884083105</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Just Believe - Single</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>2:41</v>
+        <v>3:30</v>
       </c>
       <c r="H44" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>KELS</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/just-believe/1884083104</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L44" t="str">
-        <v>Just Believe - Bailey Zimmerman</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Knife In The Heart</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/knife-in-the-heart/1857952500</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>The Afterparty</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G45" t="str">
-        <v>2:57</v>
+        <v>3:29</v>
       </c>
       <c r="H45" t="str">
-        <v>Lykke Li</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/knife-in-the-heart/1857952252</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L45" t="str">
-        <v>Knife In The Heart - Lykke Li</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Way We Touch</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/the-way-we-touch/1875315428</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>The Way We Touch - Single</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G46" t="str">
-        <v>3:09</v>
+        <v>3:01</v>
       </c>
       <c r="H46" t="str">
-        <v>Charlotte Cardin</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/charlotte-cardin/784665014</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/the-way-we-touch/1875315210</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L46" t="str">
-        <v>The Way We Touch - Charlotte Cardin</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>DANGEROUS</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/dangerous/1867202642</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>NIGHTS AFTER VAMP</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G47" t="str">
-        <v>4:06</v>
+        <v>3:01</v>
       </c>
       <c r="H47" t="str">
-        <v>Magnolia Park</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/magnolia-park/1413545983</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/dangerous/1867202638</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L47" t="str">
-        <v>DANGEROUS - Magnolia Park</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>When I Wake Up</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/when-i-wake-up/1878237800</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Dear God</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G48" t="str">
-        <v>3:33</v>
+        <v>3:30</v>
       </c>
       <c r="H48" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/when-i-wake-up/1878237662</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L48" t="str">
-        <v>When I Wake Up - The Pretty Reckless</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Breathe</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/breathe/1882808152</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Breathe - Single</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:56</v>
+        <v>2:27</v>
       </c>
       <c r="H49" t="str">
-        <v>Malcolm Todd</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/breathe/1882807987</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L49" t="str">
-        <v>Breathe - Malcolm Todd</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Minty</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/minty/1870867418</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>LINAJE</v>
       </c>
       <c r="G50" t="str">
-        <v>1:47</v>
+        <v>5:36</v>
       </c>
       <c r="H50" t="str">
-        <v>MIKE</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/mike/1253023714</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/minty/1870867411</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L50" t="str">
-        <v>Minty - MIKE</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Earth</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/earth/1870867498</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>POMPEII // UTILITY</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G51" t="str">
-        <v>1:37</v>
+        <v>3:23</v>
       </c>
       <c r="H51" t="str">
-        <v>Earl Sweatshirt</v>
+        <v>marquitos</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/earl-sweatshirt/445693504</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/earth/1870867411</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L51" t="str">
-        <v>Earth - Earl Sweatshirt</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Drink The Water</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/drink-the-water/1883172887</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G52" t="str">
-        <v>3:42</v>
+        <v>2:35</v>
       </c>
       <c r="H52" t="str">
-        <v>Jack Johnson</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/drink-the-water/1883172879</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L52" t="str">
-        <v>Drink The Water - Jack Johnson</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>A Rainy Night in Soho</v>
+        <v>Honest</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/a-rainy-night-in-soho/1878459216</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>A Rainy Night in Soho - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G53" t="str">
-        <v>4:32</v>
+        <v>3:39</v>
       </c>
       <c r="H53" t="str">
-        <v>Bruce Springsteen</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/bruce-springsteen/178834</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/a-rainy-night-in-soho/1878459215</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L53" t="str">
-        <v>A Rainy Night in Soho - Bruce Springsteen</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>If I Don't Leave I'm Gonna Stay</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/if-i-dont-leave-im-gonna-stay/1880111466</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Single</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G54" t="str">
-        <v>3:32</v>
+        <v>3:01</v>
       </c>
       <c r="H54" t="str">
-        <v>Carly Pearce</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/carly-pearce/206684981</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/if-i-dont-leave-im-gonna-stay/1880111464</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L54" t="str">
-        <v>If I Don't Leave I'm Gonna Stay - Carly Pearce</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Muchacho Alegre</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/muchacho-alegre/1880256976</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Muchacho Alegre - Single</v>
+        <v>Peaches!</v>
       </c>
       <c r="G55" t="str">
-        <v>3:08</v>
+        <v>5:00</v>
       </c>
       <c r="H55" t="str">
-        <v>Luis R Conriquez</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/luis-r-conriquez/1252271456</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/muchacho-alegre/1880256973</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L55" t="str">
-        <v>Muchacho Alegre - Luis R Conriquez</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Real Slow</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/real-slow/1869618394</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Work of Heart</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G56" t="str">
-        <v>3:22</v>
+        <v>3:36</v>
       </c>
       <c r="H56" t="str">
-        <v>Flatland Cavalry</v>
+        <v>Cannons</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/flatland-cavalry/994351172</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/real-slow/1869617637</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L56" t="str">
-        <v>Real Slow - Flatland Cavalry</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Mountain Girl</v>
+        <v>Loving One</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/mountain-girl/1870722299</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>As Is</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>2:42</v>
+        <v>3:39</v>
       </c>
       <c r="H57" t="str">
-        <v>Josiah and the Bonnevilles</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/josiah-and-the-bonnevilles/1101954493</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/mountain-girl/1870722288</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L57" t="str">
-        <v>Mountain Girl - Josiah and the Bonnevilles</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Like a Spark</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/like-a-spark/1876952751</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>American Stories</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:31</v>
+        <v>3:05</v>
       </c>
       <c r="H58" t="str">
-        <v>Rostam</v>
+        <v>Trousdale</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/like-a-spark/1876952750</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L58" t="str">
-        <v>Like a Spark - Rostam</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Cheesecake</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/cheesecake/1882526540</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>So Much To Tell You (Deluxe)</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G59" t="str">
-        <v>3:29</v>
+        <v>4:27</v>
       </c>
       <c r="H59" t="str">
-        <v>Ax and the Hatchetmen</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/ax-and-the-hatchetmen/1471855465</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/cheesecake/1882525852</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L59" t="str">
-        <v>Cheesecake - Ax and the Hatchetmen</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ALWAYS LET YOU DOWN</v>
+        <v>brb</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/always-let-you-down/1871578121</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>KINDA HARD</v>
+        <v>brb - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>3:04</v>
+        <v>2:36</v>
       </c>
       <c r="H60" t="str">
-        <v>Bilmuri</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/always-let-you-down/1871578103</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L60" t="str">
-        <v>ALWAYS LET YOU DOWN - Bilmuri</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Freakin’ Out</v>
+        <v>Euphoria</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/freakin-out/1879596115</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Freakin’ Out - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:37</v>
+        <v>3:32</v>
       </c>
       <c r="H61" t="str">
-        <v>Dexter and The Moonrocks</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/dexter-and-the-moonrocks/1581657500</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/freakin-out/1879596114</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L61" t="str">
-        <v>Freakin’ Out - Dexter and The Moonrocks</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Name in Vein</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/name-in-vein/1880069474</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Name in Vein - Single</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G62" t="str">
-        <v>3:03</v>
+        <v>2:57</v>
       </c>
       <c r="H62" t="str">
-        <v>VOILÀ</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/name-in-vein/1880069473</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L62" t="str">
-        <v>Name in Vein - VOILÀ</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>St. Catherine's Wheel</v>
+        <v>Gracie</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/st-catherines-wheel/1868804170</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Into Oblivion</v>
+        <v>F.I.G</v>
       </c>
       <c r="G63" t="str">
-        <v>4:05</v>
+        <v>2:54</v>
       </c>
       <c r="H63" t="str">
-        <v>Lamb of God</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/lamb-of-god/18758452</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/st-catherines-wheel/1868804163</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L63" t="str">
-        <v>St. Catherine's Wheel - Lamb of God</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Undefeated Champion</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/undefeated-champion/1840517120</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Sweat</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G64" t="str">
-        <v>3:34</v>
+        <v>3:02</v>
       </c>
       <c r="H64" t="str">
-        <v>Melanie C</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/undefeated-champion/1840516706</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L64" t="str">
-        <v>Undefeated Champion - Melanie C</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Pull Up</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/pull-up/1854381591</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Pull Up - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G65" t="str">
-        <v>2:35</v>
+        <v>3:14</v>
       </c>
       <c r="H65" t="str">
-        <v>Collect 200</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/collect-200/1804375505</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/pull-up/1854381590</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L65" t="str">
-        <v>Pull Up - Collect 200</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Ranjha</v>
+        <v>Trouble</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/ranjha/1882965642</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Ranjha - Single</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G66" t="str">
-        <v>3:04</v>
+        <v>3:17</v>
       </c>
       <c r="H66" t="str">
-        <v>Diljit Dosanjh</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/diljit-dosanjh/423087540</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/ranjha/1882965641</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L66" t="str">
-        <v>Ranjha - Diljit Dosanjh</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>zombies in love</v>
+        <v>judas</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/zombies-in-love/1880178176</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>zombies in love - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:53</v>
+        <v>3:31</v>
       </c>
       <c r="H67" t="str">
-        <v>paris jackson</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/zombies-in-love/1880178173</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L67" t="str">
-        <v>zombies in love - paris jackson</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Days Of Us</v>
+        <v>JINX</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/days-of-us/1868438268</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Full Circle</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>4:39</v>
+        <v>2:54</v>
       </c>
       <c r="H68" t="str">
-        <v>Tom Misch</v>
+        <v>Zacari</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/tom-misch/893237941</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/days-of-us/1868437787</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L68" t="str">
-        <v>Days Of Us - Tom Misch</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Life Of A Man</v>
+        <v>se fue</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/life-of-a-man/1882845328</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Life Of A Man - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:15</v>
+        <v>2:51</v>
       </c>
       <c r="H69" t="str">
-        <v>1Ski OG</v>
+        <v>Eddy</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/1ski-og/1801506799</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/life-of-a-man/1882845327</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L69" t="str">
-        <v>Life Of A Man - 1Ski OG</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ya No</v>
+        <v>The Blade</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/ya-no/1882115676</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Ya No - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:40</v>
+        <v>3:15</v>
       </c>
       <c r="H70" t="str">
-        <v>Marca MP</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/ya-no/1882115675</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L70" t="str">
-        <v>Ya No - Marca MP</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Do You Really Love Her</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/do-you-really-love-her/1879639011</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Do You Really Love Her - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G71" t="str">
-        <v>3:48</v>
+        <v>3:13</v>
       </c>
       <c r="H71" t="str">
-        <v>Spacey Jane</v>
+        <v>SPINALL</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/spacey-jane/1274804750</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/do-you-really-love-her/1879639009</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L71" t="str">
-        <v>Do You Really Love Her - Spacey Jane</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Relieve You</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/relieve-you/1879589717</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Relieve You - Single</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:19</v>
+        <v>2:15</v>
       </c>
       <c r="H72" t="str">
-        <v>4Fargo</v>
+        <v>ZEP</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/4fargo/1381605295</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/relieve-you/1879589716</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L72" t="str">
-        <v>Relieve You - 4Fargo</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Safety</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/safety/1878181748</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Safety - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:18</v>
+        <v>3:23</v>
       </c>
       <c r="H73" t="str">
-        <v>Lekan</v>
+        <v>Hutch</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/lekan/1540259198</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/safety/1878181738</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L73" t="str">
-        <v>Safety - Lekan</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Starlet</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/starlet/1873450846</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>LK99</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:56</v>
+        <v>5:15</v>
       </c>
       <c r="H74" t="str">
-        <v>Leven Kali</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/leven-kali/1166360470</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/starlet/1873450570</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L74" t="str">
-        <v>Starlet - Leven Kali</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Physical</v>
+        <v>Cyclone</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/physical/1883210753</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Physical - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G75" t="str">
-        <v>3:52</v>
+        <v>5:33</v>
       </c>
       <c r="H75" t="str">
-        <v>Jacquees</v>
+        <v>Gaerea</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/jacquees/386779763</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/physical/1883210752</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L75" t="str">
-        <v>Physical - Jacquees</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>i'm dying to feel alive again</v>
+        <v>Checkmate</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/im-dying-to-feel-alive-again/1880883509</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>i'm dying to feel alive again - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>4:29</v>
+        <v>4:23</v>
       </c>
       <c r="H76" t="str">
-        <v>Casper Sage</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/im-dying-to-feel-alive-again/1880883507</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L76" t="str">
-        <v>i'm dying to feel alive again - Casper Sage</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Regalito</v>
+        <v>DAVE</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/regalito/1880846653</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>TRESCENDER</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:41</v>
+        <v>2:01</v>
       </c>
       <c r="H77" t="str">
-        <v>Piso 21</v>
+        <v>Hulvey</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/piso-21/403121923</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/regalito/1880845994</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L77" t="str">
-        <v>Regalito - Piso 21</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Cruel Streak</v>
+        <v>Change</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/cruel-streak/1858689493</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>A Pound of Feathers</v>
+        <v>Change - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>4:09</v>
+        <v>2:38</v>
       </c>
       <c r="H78" t="str">
-        <v>The Black Crowes</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/the-black-crowes/2969371</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/cruel-streak/1858689485</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L78" t="str">
-        <v>Cruel Streak - The Black Crowes</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Die Young</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/die-young/1870715300</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Little Wide Open</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:52</v>
+        <v>3:05</v>
       </c>
       <c r="H79" t="str">
-        <v>Kevin Morby</v>
+        <v>Maisak</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/kevin-morby/708517315</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/die-young/1870715298</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L79" t="str">
-        <v>Die Young - Kevin Morby</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Island Girl</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/island-girl/1884461360</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Island Girl - Single</v>
+        <v>V</v>
       </c>
       <c r="G80" t="str">
-        <v>3:27</v>
+        <v>2:01</v>
       </c>
       <c r="H80" t="str">
-        <v>Pia Mia</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/pia-mia/483071062</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/island-girl/1884461354</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L80" t="str">
-        <v>Island Girl - Pia Mia</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>GIRLY THINGS</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/girly-things/1876032954</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>GIRLY THINGS - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G81" t="str">
-        <v>2:20</v>
+        <v>3:53</v>
       </c>
       <c r="H81" t="str">
-        <v>Claudia Valentina</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/claudia-valentina/1434841711</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/girly-things/1876032953</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L81" t="str">
-        <v>GIRLY THINGS - Claudia Valentina</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Looking Lovely (feat. Robin Thicke)</v>
+        <v>punchbowl</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/looking-lovely-feat-robin-thicke/1878437828</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:22</v>
+        <v>2:34</v>
       </c>
       <c r="H82" t="str">
-        <v>Shaggy</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/shaggy/68616</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/looking-lovely-feat-robin-thicke/1878437504</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L82" t="str">
-        <v>Looking Lovely (feat. Robin Thicke) - Shaggy</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tommy’s Song</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/tommys-song/1876670040</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Lovers - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:44</v>
+        <v>3:41</v>
       </c>
       <c r="H83" t="str">
-        <v>Nathaniel Rateliff</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/nathaniel-rateliff/362131302</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/tommys-song/1876670038</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L83" t="str">
-        <v>Tommy’s Song - Nathaniel Rateliff</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Rainbows</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/rainbows/1882790536</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Rainbows - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:25</v>
+        <v>2:03</v>
       </c>
       <c r="H84" t="str">
-        <v>Allison Russell</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/allison-russell/451740458</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/rainbows/1882790535</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L84" t="str">
-        <v>Rainbows - Allison Russell</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>butterflies</v>
+        <v>Free Nick</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/butterflies/1878228436</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:48</v>
+        <v>2:05</v>
       </c>
       <c r="H85" t="str">
-        <v>runo plum</v>
+        <v>Raq baby</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/butterflies/1878228434</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L85" t="str">
-        <v>butterflies - runo plum</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>You're Right</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/youre-right/1874975857</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>You're Right - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:00</v>
+        <v>3:06</v>
       </c>
       <c r="H86" t="str">
-        <v>Emma Harner</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/emma-harner/1543609198</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/youre-right/1874975856</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L86" t="str">
-        <v>You're Right - Emma Harner</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Bible Belt</v>
+        <v>Define You</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/bible-belt/1821125622</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Bible Belt - Single</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G87" t="str">
         <v>3:34</v>
       </c>
       <c r="H87" t="str">
-        <v>Baby Bugs</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/baby-bugs/1551794879</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/bible-belt/1821125621</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L87" t="str">
-        <v>Bible Belt - Baby Bugs</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Daze</v>
+        <v>If You Change</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/daze/1862607801</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Daze - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G88" t="str">
-        <v>3:22</v>
+        <v>4:41</v>
       </c>
       <c r="H88" t="str">
-        <v>Olympia Vitalis</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/daze/1862607800</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L88" t="str">
-        <v>Daze - Olympia Vitalis</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Passionfruit</v>
+        <v>What I See</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/passionfruit/1878215125</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Passionfruit - Single</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:57</v>
+        <v>2:32</v>
       </c>
       <c r="H89" t="str">
-        <v>Anish Kumar</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/passionfruit/1878215124</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L89" t="str">
-        <v>Passionfruit - Anish Kumar</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Madan</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/madan/1879822223</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Madan - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G90" t="str">
-        <v>2:56</v>
+        <v>3:47</v>
       </c>
       <c r="H90" t="str">
-        <v>Jonas Blue</v>
+        <v>Witch Post</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/jonas-blue/405728790</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/madan/1879822222</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L90" t="str">
-        <v>Madan - Jonas Blue</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Bad Bitch</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/bad-bitch/1882818210</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Bad Bitch - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>2:28</v>
+        <v>3:07</v>
       </c>
       <c r="H91" t="str">
-        <v>41</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/41/1688992229</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/bad-bitch/1882818208</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L91" t="str">
-        <v>Bad Bitch - 41</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Shame</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/shame/1874080307</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Devotion [Deluxe]</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:36</v>
+        <v>2:52</v>
       </c>
       <c r="H92" t="str">
-        <v>Sunday (1994)</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/sunday-1994/1728938785</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/shame/1874080202</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L92" t="str">
-        <v>Shame - Sunday (1994)</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>teach you to love me</v>
+        <v>Rewind It</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/teach-you-to-love-me/1883146005</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>teach you to love me - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:09</v>
+        <v>1:34</v>
       </c>
       <c r="H93" t="str">
-        <v>Hailey Picardi</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/hailey-picardi/1759557915</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/teach-you-to-love-me/1883146002</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L93" t="str">
-        <v>teach you to love me - Hailey Picardi</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Fix</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/the-fix/1882082897</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>The Fix - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:42</v>
+        <v>2:33</v>
       </c>
       <c r="H94" t="str">
-        <v>Baby J</v>
+        <v>slayr</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/baby-j/1513690931</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/the-fix/1882082895</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L94" t="str">
-        <v>The Fix - Baby J</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Hanging on Hope</v>
+        <v>Down</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/hanging-on-hope/1881749452</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Hanging on Hope - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:43</v>
+        <v>2:08</v>
       </c>
       <c r="H95" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/hanging-on-hope/1881749451</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L95" t="str">
-        <v>Hanging on Hope - Buffalo Traffic Jam</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>I Know What to Say Now</v>
+        <v>Make It Out</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/i-know-what-to-say-now/1879440545</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>I Know What to Say Now - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:18</v>
+        <v>2:17</v>
       </c>
       <c r="H96" t="str">
-        <v>Active Child</v>
+        <v>Trueblood</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/active-child/355288617</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/i-know-what-to-say-now/1879440351</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L96" t="str">
-        <v>I Know What to Say Now - Active Child</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Feel Something</v>
+        <v>better than boston</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/feel-something/1876008375</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Feel Something - Single</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:09</v>
+        <v>3:02</v>
       </c>
       <c r="H97" t="str">
-        <v>Baby Queen</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/baby-queen/336619802</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/feel-something/1876008371</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L97" t="str">
-        <v>Feel Something - Baby Queen</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>You Or Me</v>
+        <v>So Much Beauty (Around Us)</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/you-or-me/1869085528</v>
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Good God / Baad Man</v>
+        <v>So Much Beauty (Around Us) - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>5:28</v>
+        <v>2:34</v>
       </c>
       <c r="H98" t="str">
-        <v>Corrosion of Conformity</v>
+        <v>Lost Frequencies</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/corrosion-of-conformity/485858</v>
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/you-or-me/1869085524</v>
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
       </c>
       <c r="L98" t="str">
-        <v>You Or Me - Corrosion of Conformity</v>
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Mortercheyn</v>
+        <v>All I Need</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/mortercheyn/1862521946</v>
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Coronach</v>
+        <v>All I Need - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>4:18</v>
+        <v>3:06</v>
       </c>
       <c r="H99" t="str">
-        <v>Hellripper</v>
+        <v>GRiZ</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/hellripper/1229248568</v>
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/mortercheyn/1862521937</v>
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
       </c>
       <c r="L99" t="str">
-        <v>Mortercheyn - Hellripper</v>
+        <v>All I Need - GRiZ</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Rip The God</v>
+        <v>Weeping Tones</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/rip-the-god/1866957697</v>
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Peace In Place</v>
       </c>
       <c r="G100" t="str">
-        <v>5:20</v>
+        <v>2:59</v>
       </c>
       <c r="H100" t="str">
-        <v>Melvins</v>
+        <v>Poison the Well</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/rip-the-god/1866957685</v>
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
       </c>
       <c r="L100" t="str">
-        <v>Rip The God - Melvins</v>
+        <v>Weeping Tones - Poison the Well</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Who We Are</v>
+        <v>Promise You This</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/who-we-are/1879626950</v>
+        <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-20</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Who We Are - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G101" t="str">
-        <v>2:10</v>
+        <v>5:19</v>
       </c>
       <c r="H101" t="str">
-        <v>Kaleena Zanders</v>
+        <v>Exodus</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/who-we-are/1879626949</v>
+        <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
       <c r="L101" t="str">
-        <v>Who We Are - Kaleena Zanders</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Reels in 360</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/reels-in-360/1867998408</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>Dying Is The Internet</v>
-      </c>
-      <c r="G102" t="str">
-        <v>4:37</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Simo Cell</v>
-      </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/simo-cell/1001568130</v>
-      </c>
-      <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/reels-in-360/1867998295</v>
-      </c>
-      <c r="L102" t="str">
-        <v>Reels in 360 - Simo Cell</v>
+        <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1766,13 +1766,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Caught In The Echo</v>
+        <v>First Red Rays</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
+        <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D37" t="str">
         <v>2026-03-20</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Your Favorite Toy</v>
+        <v>An Undying Love for a Burning World</v>
       </c>
       <c r="G37" t="str">
-        <v>4:02</v>
+        <v>8:27</v>
       </c>
       <c r="H37" t="str">
-        <v>Foo Fighters</v>
+        <v>Neurosis</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/neurosis/18870036</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
+        <v>https://music.apple.com/us/album/first-red-rays/1882105289</v>
       </c>
       <c r="L37" t="str">
-        <v>Caught In The Echo - Foo Fighters</v>
+        <v>First Red Rays - Neurosis</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Little by Little</v>
+        <v>Caught In The Echo</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
+        <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D38" t="str">
         <v>2026-03-20</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Little by Little - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G38" t="str">
-        <v>2:34</v>
+        <v>4:02</v>
       </c>
       <c r="H38" t="str">
-        <v>Mon Rovîa</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
+        <v>https://music.apple.com/us/album/caught-in-the-echo/1877913489</v>
       </c>
       <c r="L38" t="str">
-        <v>Little by Little - Mon Rovîa</v>
+        <v>Caught In The Echo - Foo Fighters</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Montgomery County</v>
+        <v>Little by Little</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
+        <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D39" t="str">
         <v>2026-03-20</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Parker McCollum (The Deluxe Edition)</v>
+        <v>Little by Little - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:28</v>
+        <v>2:34</v>
       </c>
       <c r="H39" t="str">
-        <v>Parker McCollum</v>
+        <v>Mon Rovîa</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
+        <v>https://music.apple.com/us/artist/mon-rov%C3%AEa/1313944611</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
+        <v>https://music.apple.com/us/album/little-by-little/1879889873</v>
       </c>
       <c r="L39" t="str">
-        <v>Montgomery County - Parker McCollum</v>
+        <v>Little by Little - Mon Rovîa</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Dive Into Me</v>
+        <v>Montgomery County</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
+        <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D40" t="str">
         <v>2026-03-20</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Dive Into Me - Single</v>
+        <v>Parker McCollum (The Deluxe Edition)</v>
       </c>
       <c r="G40" t="str">
-        <v>2:46</v>
+        <v>3:28</v>
       </c>
       <c r="H40" t="str">
-        <v>Alok</v>
+        <v>Parker McCollum</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/alok/324709167</v>
+        <v>https://music.apple.com/us/artist/parker-mccollum/733165597</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
+        <v>https://music.apple.com/us/album/montgomery-county/1862624506</v>
       </c>
       <c r="L40" t="str">
-        <v>Dive Into Me - Alok</v>
+        <v>Montgomery County - Parker McCollum</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>more than just a little bit</v>
+        <v>Dive Into Me</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
+        <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D41" t="str">
         <v>2026-03-20</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>getting up to no good</v>
+        <v>Dive Into Me - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H41" t="str">
-        <v>Artemas</v>
+        <v>Alok</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
+        <v>https://music.apple.com/us/artist/alok/324709167</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
+        <v>https://music.apple.com/us/album/dive-into-me/1879789970</v>
       </c>
       <c r="L41" t="str">
-        <v>more than just a little bit - Artemas</v>
+        <v>Dive Into Me - Alok</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>WORSHIP</v>
+        <v>more than just a little bit</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/worship/1882144650</v>
+        <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D42" t="str">
         <v>2026-03-20</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>WORSHIP - Single</v>
+        <v>getting up to no good</v>
       </c>
       <c r="G42" t="str">
-        <v>2:43</v>
+        <v>2:40</v>
       </c>
       <c r="H42" t="str">
-        <v>Asake</v>
+        <v>Artemas</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/asake/1436064480</v>
+        <v>https://music.apple.com/us/artist/artemas/1300620186</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/worship/1882144646</v>
+        <v>https://music.apple.com/us/album/more-than-just-a-little-bit/1878764647</v>
       </c>
       <c r="L42" t="str">
-        <v>WORSHIP - Asake</v>
+        <v>more than just a little bit - Artemas</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Honest</v>
+        <v>WORSHIP</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/honest/1884124206</v>
+        <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D43" t="str">
         <v>2026-03-20</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Honest - Single</v>
+        <v>WORSHIP - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:22</v>
+        <v>2:43</v>
       </c>
       <c r="H43" t="str">
-        <v>Ebony Riley</v>
+        <v>Asake</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
+        <v>https://music.apple.com/us/artist/asake/1436064480</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/honest/1884124203</v>
+        <v>https://music.apple.com/us/album/worship/1882144646</v>
       </c>
       <c r="L43" t="str">
-        <v>Honest - Ebony Riley</v>
+        <v>WORSHIP - Asake</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>6ft Under</v>
+        <v>Honest</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
+        <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D44" t="str">
         <v>2026-03-20</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6ft Under - Single</v>
+        <v>Honest - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:30</v>
+        <v>3:22</v>
       </c>
       <c r="H44" t="str">
-        <v>KELS</v>
+        <v>Ebony Riley</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/kels/1536970454</v>
+        <v>https://music.apple.com/us/artist/ebony-riley/1667668245</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
+        <v>https://music.apple.com/us/album/honest/1884124203</v>
       </c>
       <c r="L44" t="str">
-        <v>6ft Under - KELS</v>
+        <v>Honest - Ebony Riley</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Maybe Again</v>
+        <v>6ft Under</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
+        <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D45" t="str">
         <v>2026-03-20</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>When The City Sleeps</v>
+        <v>6ft Under - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:29</v>
+        <v>3:30</v>
       </c>
       <c r="H45" t="str">
-        <v>Alex Isley</v>
+        <v>KELS</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
+        <v>https://music.apple.com/us/artist/kels/1536970454</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
+        <v>https://music.apple.com/us/album/6ft-under/1880796111</v>
       </c>
       <c r="L45" t="str">
-        <v>Maybe Again - Alex Isley</v>
+        <v>6ft Under - KELS</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Trigger Happy</v>
+        <v>Maybe Again</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
+        <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D46" t="str">
         <v>2026-03-20</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Attachment Theory</v>
+        <v>When The City Sleeps</v>
       </c>
       <c r="G46" t="str">
-        <v>3:01</v>
+        <v>3:29</v>
       </c>
       <c r="H46" t="str">
-        <v>Aubrie Sellers</v>
+        <v>Alex Isley</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
+        <v>https://music.apple.com/us/artist/alex-isley/566610959</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
+        <v>https://music.apple.com/us/album/maybe-again/1875112024</v>
       </c>
       <c r="L46" t="str">
-        <v>Trigger Happy - Aubrie Sellers</v>
+        <v>Maybe Again - Alex Isley</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>REAL ONES NEVER DIE</v>
+        <v>Trigger Happy</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
+        <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D47" t="str">
         <v>2026-03-20</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
+        <v>Attachment Theory</v>
       </c>
       <c r="G47" t="str">
         <v>3:01</v>
       </c>
       <c r="H47" t="str">
-        <v>Kid Cudi</v>
+        <v>Aubrie Sellers</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
+        <v>https://music.apple.com/us/artist/aubrie-sellers/1039090991</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
+        <v>https://music.apple.com/us/album/trigger-happy/1883215748</v>
       </c>
       <c r="L47" t="str">
-        <v>REAL ONES NEVER DIE - Kid Cudi</v>
+        <v>Trigger Happy - Aubrie Sellers</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>DON'T EVEN CALL</v>
+        <v>REAL ONES NEVER DIE</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
+        <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D48" t="str">
         <v>2026-03-20</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>SAME DIFFERENCE</v>
+        <v>HAVE U BN 2 HEAVEN @ NITE? - EP</v>
       </c>
       <c r="G48" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H48" t="str">
-        <v>Swae Lee</v>
+        <v>Kid Cudi</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
+        <v>https://music.apple.com/us/artist/kid-cudi/273058501</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
+        <v>https://music.apple.com/us/album/real-ones-never-die/1886092612</v>
       </c>
       <c r="L48" t="str">
-        <v>DON'T EVEN CALL - Swae Lee</v>
+        <v>REAL ONES NEVER DIE - Kid Cudi</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Runnin' On E</v>
+        <v>DON'T EVEN CALL</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
+        <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D49" t="str">
         <v>2026-03-20</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Runnin' On E - Single</v>
+        <v>SAME DIFFERENCE</v>
       </c>
       <c r="G49" t="str">
-        <v>2:27</v>
+        <v>3:30</v>
       </c>
       <c r="H49" t="str">
-        <v>Wyatt Flores</v>
+        <v>Swae Lee</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/swae-lee/922547500</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
+        <v>https://music.apple.com/us/album/dont-even-call/1885914714</v>
       </c>
       <c r="L49" t="str">
-        <v>Runnin' On E - Wyatt Flores</v>
+        <v>DON'T EVEN CALL - Swae Lee</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>FREESTYLE</v>
+        <v>Runnin' On E</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
+        <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D50" t="str">
         <v>2026-03-20</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>LINAJE</v>
+        <v>Runnin' On E - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>5:36</v>
+        <v>2:27</v>
       </c>
       <c r="H50" t="str">
-        <v>Hermanos Espinoza</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
+        <v>https://music.apple.com/us/album/runnin-on-e/1884646317</v>
       </c>
       <c r="L50" t="str">
-        <v>FREESTYLE - Hermanos Espinoza</v>
+        <v>Runnin' On E - Wyatt Flores</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Orcasitas</v>
+        <v>FREESTYLE</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
+        <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D51" t="str">
         <v>2026-03-20</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Alma De Cántaro</v>
+        <v>LINAJE</v>
       </c>
       <c r="G51" t="str">
-        <v>3:23</v>
+        <v>5:36</v>
       </c>
       <c r="H51" t="str">
-        <v>marquitos</v>
+        <v>Hermanos Espinoza</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
+        <v>https://music.apple.com/us/artist/hermanos-espinoza/1613044599</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
+        <v>https://music.apple.com/us/album/freestyle/1884623413</v>
       </c>
       <c r="L51" t="str">
-        <v>Orcasitas - marquitos</v>
+        <v>FREESTYLE - Hermanos Espinoza</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Vida Loca</v>
+        <v>Orcasitas</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
+        <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D52" t="str">
         <v>2026-03-20</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>FREE SPIRITS</v>
+        <v>Alma De Cántaro</v>
       </c>
       <c r="G52" t="str">
-        <v>2:35</v>
+        <v>3:23</v>
       </c>
       <c r="H52" t="str">
-        <v>CA7RIEL &amp; Paco Amoroso</v>
+        <v>marquitos</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
+        <v>https://music.apple.com/us/artist/marquitos/1778532119</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
+        <v>https://music.apple.com/us/album/orcasitas/1882386365</v>
       </c>
       <c r="L52" t="str">
-        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
+        <v>Orcasitas - marquitos</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Honest</v>
+        <v>Vida Loca</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/honest/1867616799</v>
+        <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D53" t="str">
         <v>2026-03-20</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>The Weight of the Woods</v>
+        <v>FREE SPIRITS</v>
       </c>
       <c r="G53" t="str">
-        <v>3:39</v>
+        <v>2:35</v>
       </c>
       <c r="H53" t="str">
-        <v>Dermot Kennedy</v>
+        <v>CA7RIEL &amp; Paco Amoroso</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ca7riel-paco-amoroso/1725159717</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/honest/1867616617</v>
+        <v>https://music.apple.com/us/album/vida-loca/1885698497</v>
       </c>
       <c r="L53" t="str">
-        <v>Honest - Dermot Kennedy</v>
+        <v>Vida Loca - CA7RIEL &amp; Paco Amoroso</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ruleta Rusa</v>
+        <v>Honest</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
+        <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D54" t="str">
         <v>2026-03-20</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>K de Karma (Apple Music Edition)</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G54" t="str">
-        <v>3:01</v>
+        <v>3:39</v>
       </c>
       <c r="H54" t="str">
-        <v>Kenia Os</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
+        <v>https://music.apple.com/us/album/honest/1867616617</v>
       </c>
       <c r="L54" t="str">
-        <v>Ruleta Rusa - Kenia Os</v>
+        <v>Honest - Dermot Kennedy</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Where There's Smoke, There's Fire</v>
+        <v>Ruleta Rusa</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
+        <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D55" t="str">
         <v>2026-03-20</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Peaches!</v>
+        <v>K de Karma (Apple Music Edition)</v>
       </c>
       <c r="G55" t="str">
-        <v>5:00</v>
+        <v>3:01</v>
       </c>
       <c r="H55" t="str">
-        <v>The Black Keys</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
+        <v>https://music.apple.com/us/artist/kenia-os/1426003035</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
+        <v>https://music.apple.com/us/album/ruleta-rusa/1868792704</v>
       </c>
       <c r="L55" t="str">
-        <v>Where There's Smoke, There's Fire - The Black Keys</v>
+        <v>Ruleta Rusa - Kenia Os</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Light as a Feather</v>
+        <v>Where There's Smoke, There's Fire</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
+        <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D56" t="str">
         <v>2026-03-20</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Everything Glows</v>
+        <v>Peaches!</v>
       </c>
       <c r="G56" t="str">
-        <v>3:36</v>
+        <v>5:00</v>
       </c>
       <c r="H56" t="str">
-        <v>Cannons</v>
+        <v>The Black Keys</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-black-keys/5893059</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
+        <v>https://music.apple.com/us/album/where-theres-smoke-theres-fire/1873477948</v>
       </c>
       <c r="L56" t="str">
-        <v>Light as a Feather - Cannons</v>
+        <v>Where There's Smoke, There's Fire - The Black Keys</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loving One</v>
+        <v>Light as a Feather</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
+        <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D57" t="str">
         <v>2026-03-20</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Loving One - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G57" t="str">
-        <v>3:39</v>
+        <v>3:36</v>
       </c>
       <c r="H57" t="str">
-        <v>People I’ve Met</v>
+        <v>Cannons</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
+        <v>https://music.apple.com/us/album/light-as-a-feather/1870989672</v>
       </c>
       <c r="L57" t="str">
-        <v>Loving One - People I’ve Met</v>
+        <v>Light as a Feather - Cannons</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Both Can Be True</v>
+        <v>Loving One</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
+        <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D58" t="str">
         <v>2026-03-20</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Both Can Be True - Single</v>
+        <v>Loving One - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:05</v>
+        <v>3:39</v>
       </c>
       <c r="H58" t="str">
-        <v>Trousdale</v>
+        <v>People I’ve Met</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/people-ive-met/1853169947</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
+        <v>https://music.apple.com/us/album/loving-one/1882487871</v>
       </c>
       <c r="L58" t="str">
-        <v>Both Can Be True - Trousdale</v>
+        <v>Loving One - People I’ve Met</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Buffalo 66</v>
+        <v>Both Can Be True</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
+        <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D59" t="str">
         <v>2026-03-20</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Jesus loves a primadonna</v>
+        <v>Both Can Be True - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>4:27</v>
+        <v>3:05</v>
       </c>
       <c r="H59" t="str">
-        <v>Nessa Barrett</v>
+        <v>Trousdale</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
+        <v>https://music.apple.com/us/album/both-can-be-true/1879642449</v>
       </c>
       <c r="L59" t="str">
-        <v>Buffalo 66 - Nessa Barrett</v>
+        <v>Both Can Be True - Trousdale</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>brb</v>
+        <v>Buffalo 66</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/brb/1884716531</v>
+        <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D60" t="str">
         <v>2026-03-20</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>brb - Single</v>
+        <v>Jesus loves a primadonna</v>
       </c>
       <c r="G60" t="str">
-        <v>2:36</v>
+        <v>4:27</v>
       </c>
       <c r="H60" t="str">
-        <v>The Two Lips</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/nessa-barrett/1525607372</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/brb/1884716521</v>
+        <v>https://music.apple.com/us/album/buffalo-66/1878795618</v>
       </c>
       <c r="L60" t="str">
-        <v>brb - The Two Lips</v>
+        <v>Buffalo 66 - Nessa Barrett</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Euphoria</v>
+        <v>brb</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
+        <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D61" t="str">
         <v>2026-03-20</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Euphoria - Single</v>
+        <v>brb - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:32</v>
+        <v>2:36</v>
       </c>
       <c r="H61" t="str">
-        <v>Talia Rae</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
+        <v>https://music.apple.com/us/album/brb/1884716521</v>
       </c>
       <c r="L61" t="str">
-        <v>Euphoria - Talia Rae</v>
+        <v>brb - The Two Lips</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>if i'm lucky</v>
+        <v>Euphoria</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
+        <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D62" t="str">
         <v>2026-03-20</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>better late than not at all - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:57</v>
+        <v>3:32</v>
       </c>
       <c r="H62" t="str">
-        <v>Chelsea Jordan</v>
+        <v>Talia Rae</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
+        <v>https://music.apple.com/us/artist/talia-rae/480784264</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
+        <v>https://music.apple.com/us/album/euphoria/1859027872</v>
       </c>
       <c r="L62" t="str">
-        <v>if i'm lucky - Chelsea Jordan</v>
+        <v>Euphoria - Talia Rae</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Gracie</v>
+        <v>if i'm lucky</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/gracie/1863525497</v>
+        <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D63" t="str">
         <v>2026-03-20</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>F.I.G</v>
+        <v>better late than not at all - EP</v>
       </c>
       <c r="G63" t="str">
-        <v>2:54</v>
+        <v>2:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Naomi Scott</v>
+        <v>Chelsea Jordan</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
+        <v>https://music.apple.com/us/artist/chelsea-jordan/1441617126</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/gracie/1863525485</v>
+        <v>https://music.apple.com/us/album/if-im-lucky/1878512860</v>
       </c>
       <c r="L63" t="str">
-        <v>Gracie - Naomi Scott</v>
+        <v>if i'm lucky - Chelsea Jordan</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Something's Not Right Here</v>
+        <v>Gracie</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
+        <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D64" t="str">
         <v>2026-03-20</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Dreaming Out Loud (Deluxe Edition)</v>
+        <v>F.I.G</v>
       </c>
       <c r="G64" t="str">
-        <v>3:02</v>
+        <v>2:54</v>
       </c>
       <c r="H64" t="str">
-        <v>OneRepublic</v>
+        <v>Naomi Scott</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
+        <v>https://music.apple.com/us/artist/naomi-scott/427283926</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
+        <v>https://music.apple.com/us/album/gracie/1863525485</v>
       </c>
       <c r="L64" t="str">
-        <v>Something's Not Right Here - OneRepublic</v>
+        <v>Gracie - Naomi Scott</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dream Chaser</v>
+        <v>down under</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
+        <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D65" t="str">
         <v>2026-03-20</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Dream Chaser</v>
+        <v>down under - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H65" t="str">
-        <v>Willie Nelson</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
+        <v>https://music.apple.com/us/album/down-under/1883127402</v>
       </c>
       <c r="L65" t="str">
-        <v>Dream Chaser - Willie Nelson</v>
+        <v>down under - Kevian Kraemer</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Trouble</v>
+        <v>Send Me A Sign</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/trouble/1876369964</v>
+        <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D66" t="str">
         <v>2026-03-20</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Girlfriend</v>
+        <v>Send Me A Sign - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:17</v>
+        <v>3:15</v>
       </c>
       <c r="H66" t="str">
-        <v>Grace Ives</v>
+        <v>Girlfriend, Wife</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
+        <v>https://music.apple.com/us/artist/girlfriend-wife/1851494782</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/trouble/1876369944</v>
+        <v>https://music.apple.com/us/album/send-me-a-sign/1883251889</v>
       </c>
       <c r="L66" t="str">
-        <v>Trouble - Grace Ives</v>
+        <v>Send Me A Sign - Girlfriend, Wife</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>judas</v>
+        <v>Something's Not Right Here</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/judas/1882829414</v>
+        <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D67" t="str">
         <v>2026-03-20</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>judas - Single</v>
+        <v>Dreaming Out Loud (Deluxe Edition)</v>
       </c>
       <c r="G67" t="str">
-        <v>3:31</v>
+        <v>3:02</v>
       </c>
       <c r="H67" t="str">
-        <v>Josiah Queen</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
+        <v>https://music.apple.com/us/artist/onerepublic/260414340</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/judas/1882829413</v>
+        <v>https://music.apple.com/us/album/somethings-not-right-here/1882090709</v>
       </c>
       <c r="L67" t="str">
-        <v>judas - Josiah Queen</v>
+        <v>Something's Not Right Here - OneRepublic</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JINX</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/jinx/1880173550</v>
+        <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D68" t="str">
         <v>2026-03-20</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>JINX - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G68" t="str">
-        <v>2:54</v>
+        <v>3:14</v>
       </c>
       <c r="H68" t="str">
-        <v>Zacari</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/jinx/1880173549</v>
+        <v>https://music.apple.com/us/album/dream-chaser/1884219677</v>
       </c>
       <c r="L68" t="str">
-        <v>JINX - Zacari</v>
+        <v>Dream Chaser - Willie Nelson</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>se fue</v>
+        <v>Trouble</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
+        <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D69" t="str">
         <v>2026-03-20</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Náufrago</v>
+        <v>Girlfriend</v>
       </c>
       <c r="G69" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H69" t="str">
-        <v>Eddy</v>
+        <v>Grace Ives</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
+        <v>https://music.apple.com/us/artist/grace-ives/1390289298</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
+        <v>https://music.apple.com/us/album/trouble/1876369944</v>
       </c>
       <c r="L69" t="str">
-        <v>se fue - Eddy</v>
+        <v>Trouble - Grace Ives</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Blade</v>
+        <v>judas</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
+        <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D70" t="str">
         <v>2026-03-20</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>The Blade - Single</v>
+        <v>judas - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:15</v>
+        <v>3:31</v>
       </c>
       <c r="H70" t="str">
-        <v>Kingfishr</v>
+        <v>Josiah Queen</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
+        <v>https://music.apple.com/us/artist/josiah-queen/1498117530</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
+        <v>https://music.apple.com/us/album/judas/1882829413</v>
       </c>
       <c r="L70" t="str">
-        <v>The Blade - Kingfishr</v>
+        <v>judas - Josiah Queen</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Metric Rules</v>
+        <v>JINX</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
+        <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D71" t="str">
         <v>2026-03-20</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>When Lagos Sleeps - EP</v>
+        <v>JINX - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:13</v>
+        <v>2:54</v>
       </c>
       <c r="H71" t="str">
-        <v>SPINALL</v>
+        <v>Zacari</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/zacari/1027112445</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
+        <v>https://music.apple.com/us/album/jinx/1880173549</v>
       </c>
       <c r="L71" t="str">
-        <v>Metric Rules - SPINALL</v>
+        <v>JINX - Zacari</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>FIGURE IT OUT</v>
+        <v>se fue</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
+        <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D72" t="str">
         <v>2026-03-20</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>FIGURE IT OUT - Single</v>
+        <v>Náufrago</v>
       </c>
       <c r="G72" t="str">
-        <v>2:15</v>
+        <v>2:51</v>
       </c>
       <c r="H72" t="str">
-        <v>ZEP</v>
+        <v>Eddy</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/zep/1582892045</v>
+        <v>https://music.apple.com/us/artist/eddy/1779584924</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
+        <v>https://music.apple.com/us/album/se-fue/1876355962</v>
       </c>
       <c r="L72" t="str">
-        <v>FIGURE IT OUT - ZEP</v>
+        <v>se fue - Eddy</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Coasting (Piano Session)</v>
+        <v>The Blade</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
+        <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D73" t="str">
         <v>2026-03-20</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Coasting (Piano Session) - Single</v>
+        <v>The Blade - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:23</v>
+        <v>3:15</v>
       </c>
       <c r="H73" t="str">
-        <v>Hutch</v>
+        <v>Kingfishr</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
+        <v>https://music.apple.com/us/artist/kingfishr/1616516476</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
+        <v>https://music.apple.com/us/album/the-blade/1884066685</v>
       </c>
       <c r="L73" t="str">
-        <v>Coasting (Piano Session) - Hutch</v>
+        <v>The Blade - Kingfishr</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
+        <v>Metric Rules</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
+        <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D74" t="str">
         <v>2026-03-20</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
+        <v>When Lagos Sleeps - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>5:15</v>
+        <v>3:13</v>
       </c>
       <c r="H74" t="str">
-        <v>MJ Cole</v>
+        <v>SPINALL</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
+        <v>https://music.apple.com/us/album/metric-rules/1885609347</v>
       </c>
       <c r="L74" t="str">
-        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
+        <v>Metric Rules - SPINALL</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Cyclone</v>
+        <v>FIGURE IT OUT</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
+        <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D75" t="str">
         <v>2026-03-20</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Loss</v>
+        <v>FIGURE IT OUT - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>5:33</v>
+        <v>2:15</v>
       </c>
       <c r="H75" t="str">
-        <v>Gaerea</v>
+        <v>ZEP</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/zep/1582892045</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
+        <v>https://music.apple.com/us/album/figure-it-out/1882873713</v>
       </c>
       <c r="L75" t="str">
-        <v>Cyclone - Gaerea</v>
+        <v>FIGURE IT OUT - ZEP</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Checkmate</v>
+        <v>Coasting (Piano Session)</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
+        <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D76" t="str">
         <v>2026-03-20</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Checkmate - Single</v>
+        <v>Coasting (Piano Session) - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>4:23</v>
+        <v>3:23</v>
       </c>
       <c r="H76" t="str">
-        <v>Blue Medusa</v>
+        <v>Hutch</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
+        <v>https://music.apple.com/us/artist/hutch/1852060852</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
+        <v>https://music.apple.com/us/album/coasting-piano-session/1880328048</v>
       </c>
       <c r="L76" t="str">
-        <v>Checkmate - Blue Medusa</v>
+        <v>Coasting (Piano Session) - Hutch</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DAVE</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub]</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/dave/1881700152</v>
+        <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D77" t="str">
         <v>2026-03-20</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>DAVE - Single</v>
+        <v>Still Sincere (MK Dub) [feat. PinkPantheress] - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:01</v>
+        <v>5:15</v>
       </c>
       <c r="H77" t="str">
-        <v>Hulvey</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/dave/1881700151</v>
+        <v>https://music.apple.com/us/album/still-sincere-feat-pinkpantheress-mk-dub/1882054676</v>
       </c>
       <c r="L77" t="str">
-        <v>DAVE - Hulvey</v>
+        <v>Still Sincere (feat. PinkPantheress) [MK Dub] - MJ Cole</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Change</v>
+        <v>Cyclone</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/change/1880857720</v>
+        <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D78" t="str">
         <v>2026-03-20</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Change - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G78" t="str">
-        <v>2:38</v>
+        <v>5:33</v>
       </c>
       <c r="H78" t="str">
-        <v>Stephen Stanley</v>
+        <v>Gaerea</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/change/1880857716</v>
+        <v>https://music.apple.com/us/album/cyclone/1843578156</v>
       </c>
       <c r="L78" t="str">
-        <v>Change - Stephen Stanley</v>
+        <v>Cyclone - Gaerea</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Te Entiendo</v>
+        <v>Checkmate</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
+        <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D79" t="str">
         <v>2026-03-20</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Te Entiendo - Single</v>
+        <v>Checkmate - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:05</v>
+        <v>4:23</v>
       </c>
       <c r="H79" t="str">
-        <v>Maisak</v>
+        <v>Blue Medusa</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
+        <v>https://music.apple.com/us/artist/blue-medusa/1882057979</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
+        <v>https://music.apple.com/us/album/checkmate/1882117111</v>
       </c>
       <c r="L79" t="str">
-        <v>Te Entiendo - Maisak</v>
+        <v>Checkmate - Blue Medusa</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>CHEVROLET 90</v>
+        <v>DAVE</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
+        <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D80" t="str">
         <v>2026-03-20</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>V</v>
+        <v>DAVE - Single</v>
       </c>
       <c r="G80" t="str">
         <v>2:01</v>
       </c>
       <c r="H80" t="str">
-        <v>Rey Quinto</v>
+        <v>Hulvey</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
+        <v>https://music.apple.com/us/artist/hulvey/1438377315</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
+        <v>https://music.apple.com/us/album/dave/1881700151</v>
       </c>
       <c r="L80" t="str">
-        <v>CHEVROLET 90 - Rey Quinto</v>
+        <v>DAVE - Hulvey</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tirabalas</v>
+        <v>Change</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
+        <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D81" t="str">
         <v>2026-03-20</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>ESSENCE #10 (Deluxe)</v>
+        <v>Change - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:53</v>
+        <v>2:38</v>
       </c>
       <c r="H81" t="str">
-        <v>Hans el Oso</v>
+        <v>Stephen Stanley</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
+        <v>https://music.apple.com/us/artist/stephen-stanley/28074609</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
+        <v>https://music.apple.com/us/album/change/1880857716</v>
       </c>
       <c r="L81" t="str">
-        <v>Tirabalas - Hans el Oso</v>
+        <v>Change - Stephen Stanley</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>punchbowl</v>
+        <v>Te Entiendo</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
+        <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D82" t="str">
         <v>2026-03-20</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>punchbowl - Single</v>
+        <v>Te Entiendo - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:34</v>
+        <v>3:05</v>
       </c>
       <c r="H82" t="str">
-        <v>Julio Caesar</v>
+        <v>Maisak</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/maisak/1610652984</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
+        <v>https://music.apple.com/us/album/te-entiendo/1882386238</v>
       </c>
       <c r="L82" t="str">
-        <v>punchbowl - Julio Caesar</v>
+        <v>Te Entiendo - Maisak</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Wild Ride</v>
+        <v>CHEVROLET 90</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
+        <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D83" t="str">
         <v>2026-03-20</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Wild Ride - Single</v>
+        <v>V</v>
       </c>
       <c r="G83" t="str">
-        <v>3:41</v>
+        <v>2:01</v>
       </c>
       <c r="H83" t="str">
-        <v>Durand Bernarr</v>
+        <v>Rey Quinto</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
+        <v>https://music.apple.com/us/artist/rey-quinto/1715073363</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
+        <v>https://music.apple.com/us/album/chevrolet-90/1879599141</v>
       </c>
       <c r="L83" t="str">
-        <v>Wild Ride - Durand Bernarr</v>
+        <v>CHEVROLET 90 - Rey Quinto</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Lamb Chop</v>
+        <v>Tirabalas</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
+        <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D84" t="str">
         <v>2026-03-20</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Lamb Chop - Single</v>
+        <v>ESSENCE #10 (Deluxe)</v>
       </c>
       <c r="G84" t="str">
-        <v>2:03</v>
+        <v>3:53</v>
       </c>
       <c r="H84" t="str">
-        <v>Chuckyy</v>
+        <v>Hans el Oso</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
+        <v>https://music.apple.com/us/artist/hans-el-oso/1619227662</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
+        <v>https://music.apple.com/us/album/tirabalas/1877963565</v>
       </c>
       <c r="L84" t="str">
-        <v>Lamb Chop - Chuckyy</v>
+        <v>Tirabalas - Hans el Oso</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Free Nick</v>
+        <v>punchbowl</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
+        <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D85" t="str">
         <v>2026-03-20</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Free Nick - Single</v>
+        <v>punchbowl - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:05</v>
+        <v>2:34</v>
       </c>
       <c r="H85" t="str">
-        <v>Raq baby</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
+        <v>https://music.apple.com/us/album/punchbowl/1883156073</v>
       </c>
       <c r="L85" t="str">
-        <v>Free Nick - Raq baby</v>
+        <v>punchbowl - Julio Caesar</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Make Me Brand New</v>
+        <v>Wild Ride</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
+        <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D86" t="str">
         <v>2026-03-20</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Make Me Brand New - Single</v>
+        <v>Wild Ride - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:06</v>
+        <v>3:41</v>
       </c>
       <c r="H86" t="str">
-        <v>Dante’ Pride</v>
+        <v>Durand Bernarr</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
+        <v>https://music.apple.com/us/artist/durand-bernarr/584124023</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
+        <v>https://music.apple.com/us/album/wild-ride/1884728580</v>
       </c>
       <c r="L86" t="str">
-        <v>Make Me Brand New - Dante’ Pride</v>
+        <v>Wild Ride - Durand Bernarr</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Define You</v>
+        <v>Lamb Chop</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/define-you/1877189744</v>
+        <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D87" t="str">
         <v>2026-03-20</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Define You - Single</v>
+        <v>Lamb Chop - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:34</v>
+        <v>2:03</v>
       </c>
       <c r="H87" t="str">
-        <v>Luca Fogale</v>
+        <v>Chuckyy</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/chuckyy/1703210537</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/define-you/1877189743</v>
+        <v>https://music.apple.com/us/album/lamb-chop/1881677465</v>
       </c>
       <c r="L87" t="str">
-        <v>Define You - Luca Fogale</v>
+        <v>Lamb Chop - Chuckyy</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>If You Change</v>
+        <v>Free Nick</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
+        <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D88" t="str">
         <v>2026-03-20</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Roses</v>
+        <v>Free Nick - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>4:41</v>
+        <v>2:05</v>
       </c>
       <c r="H88" t="str">
-        <v>Widowspeak</v>
+        <v>Raq baby</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/raq-baby/1712935965</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
+        <v>https://music.apple.com/us/album/free-nick/1881667216</v>
       </c>
       <c r="L88" t="str">
-        <v>If You Change - Widowspeak</v>
+        <v>Free Nick - Raq baby</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>What I See</v>
+        <v>Make Me Brand New</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
+        <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D89" t="str">
         <v>2026-03-20</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>SYNY 3 Act II - Single</v>
+        <v>Make Me Brand New - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>2:32</v>
+        <v>3:06</v>
       </c>
       <c r="H89" t="str">
-        <v>See You Next Year</v>
+        <v>Dante’ Pride</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
+        <v>https://music.apple.com/us/artist/dante-pride/1175536450</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
+        <v>https://music.apple.com/us/album/make-me-brand-new/1878525833</v>
       </c>
       <c r="L89" t="str">
-        <v>What I See - See You Next Year</v>
+        <v>Make Me Brand New - Dante’ Pride</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Witching Hour</v>
+        <v>Define You</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
+        <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D90" t="str">
         <v>2026-03-20</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Butterfly</v>
+        <v>Define You - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="H90" t="str">
-        <v>Witch Post</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
+        <v>https://music.apple.com/us/album/define-you/1877189743</v>
       </c>
       <c r="L90" t="str">
-        <v>Witching Hour - Witch Post</v>
+        <v>Define You - Luca Fogale</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Actin' Tough</v>
+        <v>If You Change</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
+        <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D91" t="str">
         <v>2026-03-20</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Actin' Tough - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G91" t="str">
-        <v>3:07</v>
+        <v>4:41</v>
       </c>
       <c r="H91" t="str">
-        <v>Dean Turnley</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
+        <v>https://music.apple.com/us/album/if-you-change/1880416141</v>
       </c>
       <c r="L91" t="str">
-        <v>Actin' Tough - Dean Turnley</v>
+        <v>If You Change - Widowspeak</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Coração - A COLORS SHOW</v>
+        <v>What I See</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
+        <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D92" t="str">
         <v>2026-03-20</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Coração - A COLORS SHOW - Single</v>
+        <v>SYNY 3 Act II - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>2:52</v>
+        <v>2:32</v>
       </c>
       <c r="H92" t="str">
-        <v>Anais Cardot</v>
+        <v>See You Next Year</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/see-you-next-year/1624754980</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
+        <v>https://music.apple.com/us/album/what-i-see/1882879433</v>
       </c>
       <c r="L92" t="str">
-        <v>Coração - A COLORS SHOW - Anais Cardot</v>
+        <v>What I See - See You Next Year</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Rewind It</v>
+        <v>Witching Hour</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
+        <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D93" t="str">
         <v>2026-03-20</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Rewind It - Single</v>
+        <v>Butterfly</v>
       </c>
       <c r="G93" t="str">
-        <v>1:34</v>
+        <v>3:47</v>
       </c>
       <c r="H93" t="str">
-        <v>Nino Paid</v>
+        <v>Witch Post</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
+        <v>https://music.apple.com/us/artist/witch-post/1774955367</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
+        <v>https://music.apple.com/us/album/witching-hour/1870760649</v>
       </c>
       <c r="L93" t="str">
-        <v>Rewind It - Nino Paid</v>
+        <v>Witching Hour - Witch Post</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Turn It Up</v>
+        <v>Actin' Tough</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
+        <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D94" t="str">
         <v>2026-03-20</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Turn It Up - Single</v>
+        <v>Actin' Tough - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:33</v>
+        <v>3:07</v>
       </c>
       <c r="H94" t="str">
-        <v>slayr</v>
+        <v>Dean Turnley</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/dean-turnley/1561296990</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
+        <v>https://music.apple.com/us/album/actin-tough/1881996384</v>
       </c>
       <c r="L94" t="str">
-        <v>Turn It Up - slayr</v>
+        <v>Actin' Tough - Dean Turnley</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Down</v>
+        <v>Coração - A COLORS SHOW</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/down/1884531560</v>
+        <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D95" t="str">
         <v>2026-03-20</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Down - Single</v>
+        <v>Coração - A COLORS SHOW - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>2:08</v>
+        <v>2:52</v>
       </c>
       <c r="H95" t="str">
-        <v>MexikoDro</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/down/1884531558</v>
+        <v>https://music.apple.com/us/album/cora%C3%A7%C3%A3o-a-colors-show/1880127529</v>
       </c>
       <c r="L95" t="str">
-        <v>Down - MexikoDro</v>
+        <v>Coração - A COLORS SHOW - Anais Cardot</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Make It Out</v>
+        <v>Rewind It</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
+        <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D96" t="str">
         <v>2026-03-20</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Make It Out - Single</v>
+        <v>Rewind It - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>2:17</v>
+        <v>1:34</v>
       </c>
       <c r="H96" t="str">
-        <v>Trueblood</v>
+        <v>Nino Paid</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
+        <v>https://music.apple.com/us/artist/nino-paid/1636385121</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
+        <v>https://music.apple.com/us/album/rewind-it/1884966848</v>
       </c>
       <c r="L96" t="str">
-        <v>Make It Out - Trueblood</v>
+        <v>Rewind It - Nino Paid</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>better than boston</v>
+        <v>Turn It Up</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
+        <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D97" t="str">
         <v>2026-03-20</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>better than boston - Single</v>
+        <v>Turn It Up - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:02</v>
+        <v>2:33</v>
       </c>
       <c r="H97" t="str">
-        <v>Tom Siletto</v>
+        <v>slayr</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
+        <v>https://music.apple.com/us/album/turn-it-up/1885664393</v>
       </c>
       <c r="L97" t="str">
-        <v>better than boston - Tom Siletto</v>
+        <v>Turn It Up - slayr</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>So Much Beauty (Around Us)</v>
+        <v>Down</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+        <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D98" t="str">
         <v>2026-03-20</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>So Much Beauty (Around Us) - Single</v>
+        <v>Down - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:34</v>
+        <v>2:08</v>
       </c>
       <c r="H98" t="str">
-        <v>Lost Frequencies</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+        <v>https://music.apple.com/us/album/down/1884531558</v>
       </c>
       <c r="L98" t="str">
-        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+        <v>Down - MexikoDro</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>All I Need</v>
+        <v>Make It Out</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+        <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D99" t="str">
         <v>2026-03-20</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>All I Need - Single</v>
+        <v>Make It Out - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>3:06</v>
+        <v>2:17</v>
       </c>
       <c r="H99" t="str">
-        <v>GRiZ</v>
+        <v>Trueblood</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/griz/980722716</v>
+        <v>https://music.apple.com/us/artist/trueblood/1688100658</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+        <v>https://music.apple.com/us/album/make-it-out/1883117392</v>
       </c>
       <c r="L99" t="str">
-        <v>All I Need - GRiZ</v>
+        <v>Make It Out - Trueblood</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Weeping Tones</v>
+        <v>better than boston</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+        <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D100" t="str">
         <v>2026-03-20</v>
@@ -4175,68 +4175,182 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Peace In Place</v>
+        <v>better than boston - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>2:59</v>
+        <v>3:02</v>
       </c>
       <c r="H100" t="str">
-        <v>Poison the Well</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+        <v>https://music.apple.com/us/album/better-than-boston/1885587016</v>
       </c>
       <c r="L100" t="str">
-        <v>Weeping Tones - Poison the Well</v>
+        <v>better than boston - Tom Siletto</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>So Much Beauty (Around Us)</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>So Much Beauty (Around Us) - Single</v>
+      </c>
+      <c r="G101" t="str">
+        <v>2:34</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Lost Frequencies</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/lost-frequencies/877792512</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/so-much-beauty-around-us/1880038907</v>
+      </c>
+      <c r="L101" t="str">
+        <v>So Much Beauty (Around Us) - Lost Frequencies</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>All I Need</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>All I Need - Single</v>
+      </c>
+      <c r="G102" t="str">
+        <v>3:06</v>
+      </c>
+      <c r="H102" t="str">
+        <v>GRiZ</v>
+      </c>
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://music.apple.com/us/artist/griz/980722716</v>
+      </c>
+      <c r="K102" t="str">
+        <v>https://music.apple.com/us/album/all-i-need/1878185371</v>
+      </c>
+      <c r="L102" t="str">
+        <v>All I Need - GRiZ</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Weeping Tones</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>Peace In Place</v>
+      </c>
+      <c r="G103" t="str">
+        <v>2:59</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Poison the Well</v>
+      </c>
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
+        <v>https://music.apple.com/us/artist/poison-the-well/1710155</v>
+      </c>
+      <c r="K103" t="str">
+        <v>https://music.apple.com/us/album/weeping-tones/1863532634</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Weeping Tones - Poison the Well</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>Promise You This</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-03-20</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D104" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
         <v>Goliath</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G104" t="str">
         <v>5:19</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H104" t="str">
         <v>Exodus</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I104" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J104" t="str">
         <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K104" t="str">
         <v>https://music.apple.com/us/album/promise-you-this/1862225385</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L104" t="str">
         <v>Promise You This - Exodus</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-03-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/swim/1868862384</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/click-clack-symphony-feat-hans-zimmer/1871085694</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/loving-life-again/1869436847</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/rethink-some-things/1862634795</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/trankaito/1886206698</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/leak-it/1881685399</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/luvagirl/1882867562</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/d33p3r/1876874356</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/let-king-tonka-talk/1886559004</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/dont-hate-me/1886125791</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/pongo/1882157609</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/botero/1884672859</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/distance/1882713727</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/ocean-in-the-desert/1878421692</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/riptides/1878362645</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/2-0/1868862380</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/6ixer-party/1880492403</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/highest/1882162060</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/better-than-yours-feat-youngboy-never-broke-again/1885598075</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/so-what/1870703328</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/girl-of-your-dreams-live-at-apple-music-radio/1886190880</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/running-to-pain/1876521161</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/pinterest-spanish/1885472606</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/business-personal-intro/1886539096</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/bird-flu/1884792159</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/lighter/1884704638</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/wide-awake/1881700925</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/dont-make-me-love-u/1885895137</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/dinner-party/1884418570</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/normal/1868862387</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/die-living/1884752889</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/heaven-on-earth/1882808097</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/an-apple-a-day/1885590382</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/out-late/1884478039</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/be-with-you/1885607727</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/first-red-rays/1882105294</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/caught-in-the-echo/1877913491</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/little-by-little/1879889876</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/montgomery-county/1862624758</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/dive-into-me/1879790158</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/more-than-just-a-little-bit/1878764653</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/worship/1882144650</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/honest/1884124206</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/6ft-under/1880796117</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/maybe-again/1875112466</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/trigger-happy/1883215750</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/real-ones-never-die/1886092613</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/dont-even-call/1885914732</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/runnin-on-e/1884646318</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/freestyle/1884623617</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/orcasitas/1882386609</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/vida-loca/1885698516</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/honest/1867616799</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/ruleta-rusa/1868792929</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/where-theres-smoke-theres-fire/1873477949</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/light-as-a-feather/1870989894</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/loving-one/1882487874</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/both-can-be-true/1879642452</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/buffalo-66/1878795630</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/brb/1884716531</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/euphoria/1859028065</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/if-im-lucky/1878512865</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/gracie/1863525497</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/down-under/1883127406</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/send-me-a-sign/1883251911</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/somethings-not-right-here/1882090886</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/dream-chaser/1884219678</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/trouble/1876369964</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/judas/1882829414</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/jinx/1880173550</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/se-fue/1876355980</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/the-blade/1884066958</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/metric-rules/1885609351</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/figure-it-out/1882873714</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/coasting-piano-session/1880328049</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/still-sincere-feat-pinkpantheress-mk-dub/1882054680</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/cyclone/1843578165</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/checkmate/1882117113</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/dave/1881700152</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/change/1880857720</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/te-entiendo/1882386240</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/chevrolet-90/1879599158</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/tirabalas/1877963582</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/punchbowl/1883156074</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/wild-ride/1884728581</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/lamb-chop/1881677466</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/free-nick/1881667330</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/make-me-brand-new/1878525836</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/define-you/1877189744</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/if-you-change/1880416153</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/what-i-see/1882879437</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/witching-hour/1870760652</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/actin-tough/1881996627</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/cora%C3%A7%C3%A3o-a-colors-show/1880127530</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/rewind-it/1884966852</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/turn-it-up/1885664396</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/down/1884531560</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/make-it-out/1883117489</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/better-than-boston/1885587018</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/so-much-beauty-around-us/1880038915</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/all-i-need/1878185372</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/weeping-tones/1863532922</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/promise-you-this/1862225614</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-03-20</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E104" t="str">
         <v/>
